--- a/data/H131_20260617_18.xlsx
+++ b/data/H131_20260617_18.xlsx
@@ -237,7 +237,7 @@
         <v>1092.0</v>
       </c>
       <c r="J2" t="n">
-        <v>829.0</v>
+        <v>838.0</v>
       </c>
       <c r="K2" t="n">
         <v>1.0</v>
@@ -249,10 +249,10 @@
         <v>0.0</v>
       </c>
       <c r="N2" t="n">
-        <v>829.0</v>
+        <v>838.0</v>
       </c>
       <c r="O2" t="n">
-        <v>400.0</v>
+        <v>409.0</v>
       </c>
       <c r="P2" t="n">
         <v>427.0</v>
@@ -308,7 +308,7 @@
         <v>291.0</v>
       </c>
       <c r="J3" t="n">
-        <v>242.0</v>
+        <v>247.0</v>
       </c>
       <c r="K3" t="n">
         <v>1.0</v>
@@ -320,13 +320,13 @@
         <v>0.0</v>
       </c>
       <c r="N3" t="n">
-        <v>242.0</v>
+        <v>247.0</v>
       </c>
       <c r="O3" t="n">
-        <v>85.0</v>
+        <v>88.0</v>
       </c>
       <c r="P3" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="Q3" t="n">
         <v>3.0</v>
@@ -379,7 +379,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" t="n">
-        <v>503.0</v>
+        <v>543.0</v>
       </c>
       <c r="K4" t="n">
         <v>1.0</v>
@@ -391,13 +391,13 @@
         <v>0.0</v>
       </c>
       <c r="N4" t="n">
-        <v>503.0</v>
+        <v>543.0</v>
       </c>
       <c r="O4" t="n">
-        <v>197.0</v>
+        <v>222.0</v>
       </c>
       <c r="P4" t="n">
-        <v>306.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0</v>
@@ -450,7 +450,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" t="n">
-        <v>420.0</v>
+        <v>438.0</v>
       </c>
       <c r="K5" t="n">
         <v>1.0</v>
@@ -462,13 +462,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" t="n">
-        <v>420.0</v>
+        <v>438.0</v>
       </c>
       <c r="O5" t="n">
-        <v>176.0</v>
+        <v>193.0</v>
       </c>
       <c r="P5" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="Q5" t="n">
         <v>1.0</v>
@@ -521,7 +521,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" t="n">
-        <v>586.0</v>
+        <v>636.0</v>
       </c>
       <c r="K6" t="n">
         <v>1.0</v>
@@ -533,13 +533,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" t="n">
-        <v>586.0</v>
+        <v>636.0</v>
       </c>
       <c r="O6" t="n">
-        <v>254.0</v>
+        <v>290.0</v>
       </c>
       <c r="P6" t="n">
-        <v>332.0</v>
+        <v>346.0</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0</v>
@@ -592,7 +592,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" t="n">
-        <v>363.0</v>
+        <v>367.0</v>
       </c>
       <c r="K7" t="n">
         <v>1.0</v>
@@ -604,13 +604,13 @@
         <v>0.0</v>
       </c>
       <c r="N7" t="n">
-        <v>363.0</v>
+        <v>367.0</v>
       </c>
       <c r="O7" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="P7" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0</v>
@@ -734,7 +734,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" t="n">
-        <v>354.0</v>
+        <v>376.0</v>
       </c>
       <c r="K9" t="n">
         <v>1.0</v>
@@ -746,13 +746,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" t="n">
-        <v>354.0</v>
+        <v>376.0</v>
       </c>
       <c r="O9" t="n">
-        <v>171.0</v>
+        <v>184.0</v>
       </c>
       <c r="P9" t="n">
-        <v>183.0</v>
+        <v>192.0</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0</v>
@@ -805,25 +805,25 @@
         <v>311.0</v>
       </c>
       <c r="J10" t="n">
+        <v>229.0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N10" t="n">
         <v>228.0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>227.0</v>
       </c>
       <c r="O10" t="n">
         <v>82.0</v>
       </c>
       <c r="P10" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="Q10" t="n">
         <v>21.0</v>
@@ -947,7 +947,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" t="n">
-        <v>609.0</v>
+        <v>632.0</v>
       </c>
       <c r="K12" t="n">
         <v>1.0</v>
@@ -959,13 +959,13 @@
         <v>0.0</v>
       </c>
       <c r="N12" t="n">
-        <v>609.0</v>
+        <v>632.0</v>
       </c>
       <c r="O12" t="n">
-        <v>315.0</v>
+        <v>331.0</v>
       </c>
       <c r="P12" t="n">
-        <v>294.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q12" t="n">
         <v>0.0</v>
@@ -1018,7 +1018,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" t="n">
-        <v>880.0</v>
+        <v>909.0</v>
       </c>
       <c r="K13" t="n">
         <v>1.0</v>
@@ -1030,13 +1030,13 @@
         <v>0.0</v>
       </c>
       <c r="N13" t="n">
-        <v>880.0</v>
+        <v>909.0</v>
       </c>
       <c r="O13" t="n">
-        <v>437.0</v>
+        <v>451.0</v>
       </c>
       <c r="P13" t="n">
-        <v>443.0</v>
+        <v>458.0</v>
       </c>
       <c r="Q13" t="n">
         <v>0.0</v>
@@ -1089,7 +1089,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" t="n">
-        <v>549.0</v>
+        <v>653.0</v>
       </c>
       <c r="K14" t="n">
         <v>1.0</v>
@@ -1101,13 +1101,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" t="n">
-        <v>549.0</v>
+        <v>653.0</v>
       </c>
       <c r="O14" t="n">
-        <v>166.0</v>
+        <v>266.0</v>
       </c>
       <c r="P14" t="n">
-        <v>383.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q14" t="n">
         <v>0.0</v>
@@ -1116,7 +1116,7 @@
         <v>0.0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T14" t="n">
         <v>0.0</v>
@@ -1128,7 +1128,7 @@
         <v>0.0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
@@ -1299,10 +1299,10 @@
         <v>830.0</v>
       </c>
       <c r="I17" t="n">
-        <v>822.0</v>
+        <v>829.0</v>
       </c>
       <c r="J17" t="n">
-        <v>468.0</v>
+        <v>500.0</v>
       </c>
       <c r="K17" t="n">
         <v>1.0</v>
@@ -1314,13 +1314,13 @@
         <v>0.0</v>
       </c>
       <c r="N17" t="n">
-        <v>468.0</v>
+        <v>500.0</v>
       </c>
       <c r="O17" t="n">
-        <v>218.0</v>
+        <v>234.0</v>
       </c>
       <c r="P17" t="n">
-        <v>250.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q17" t="n">
         <v>0.0</v>
@@ -1332,7 +1332,7 @@
         <v>1.0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U17" t="n">
         <v>0.0</v>
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -1373,7 +1373,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" t="n">
-        <v>1041.0</v>
+        <v>1071.0</v>
       </c>
       <c r="K18" t="n">
         <v>1.0</v>
@@ -1385,13 +1385,13 @@
         <v>0.0</v>
       </c>
       <c r="N18" t="n">
-        <v>1041.0</v>
+        <v>1071.0</v>
       </c>
       <c r="O18" t="n">
-        <v>523.0</v>
+        <v>547.0</v>
       </c>
       <c r="P18" t="n">
-        <v>518.0</v>
+        <v>524.0</v>
       </c>
       <c r="Q18" t="n">
         <v>0.0</v>
@@ -1444,7 +1444,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" t="n">
-        <v>398.0</v>
+        <v>555.0</v>
       </c>
       <c r="K19" t="n">
         <v>1.0</v>
@@ -1456,25 +1456,25 @@
         <v>0.0</v>
       </c>
       <c r="N19" t="n">
-        <v>398.0</v>
+        <v>555.0</v>
       </c>
       <c r="O19" t="n">
-        <v>219.0</v>
+        <v>292.0</v>
       </c>
       <c r="P19" t="n">
-        <v>179.0</v>
+        <v>263.0</v>
       </c>
       <c r="Q19" t="n">
         <v>0.0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U19" t="n">
         <v>0.0</v>
@@ -1483,7 +1483,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="20">
@@ -1515,7 +1515,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" t="n">
-        <v>660.0</v>
+        <v>803.0</v>
       </c>
       <c r="K20" t="n">
         <v>1.0</v>
@@ -1527,13 +1527,13 @@
         <v>1.0</v>
       </c>
       <c r="N20" t="n">
-        <v>659.0</v>
+        <v>802.0</v>
       </c>
       <c r="O20" t="n">
-        <v>356.0</v>
+        <v>438.0</v>
       </c>
       <c r="P20" t="n">
-        <v>304.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q20" t="n">
         <v>0.0</v>
@@ -1586,7 +1586,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" t="n">
-        <v>573.0</v>
+        <v>609.0</v>
       </c>
       <c r="K21" t="n">
         <v>1.0</v>
@@ -1598,13 +1598,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" t="n">
-        <v>573.0</v>
+        <v>609.0</v>
       </c>
       <c r="O21" t="n">
-        <v>275.0</v>
+        <v>308.0</v>
       </c>
       <c r="P21" t="n">
-        <v>298.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q21" t="n">
         <v>0.0</v>
@@ -1657,7 +1657,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" t="n">
-        <v>744.0</v>
+        <v>763.0</v>
       </c>
       <c r="K22" t="n">
         <v>1.0</v>
@@ -1669,13 +1669,13 @@
         <v>0.0</v>
       </c>
       <c r="N22" t="n">
-        <v>744.0</v>
+        <v>763.0</v>
       </c>
       <c r="O22" t="n">
-        <v>427.0</v>
+        <v>435.0</v>
       </c>
       <c r="P22" t="n">
-        <v>317.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q22" t="n">
         <v>0.0</v>
@@ -1728,7 +1728,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="K23" t="n">
         <v>1.0</v>
@@ -1737,7 +1737,7 @@
         <v>1.0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N23" t="n">
         <v>254.0</v>
@@ -1746,7 +1746,7 @@
         <v>117.0</v>
       </c>
       <c r="P23" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0</v>
@@ -1799,7 +1799,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" t="n">
-        <v>431.0</v>
+        <v>524.0</v>
       </c>
       <c r="K24" t="n">
         <v>1.0</v>
@@ -1811,20 +1811,20 @@
         <v>0.0</v>
       </c>
       <c r="N24" t="n">
-        <v>431.0</v>
+        <v>524.0</v>
       </c>
       <c r="O24" t="n">
-        <v>248.0</v>
+        <v>297.0</v>
       </c>
       <c r="P24" t="n">
-        <v>177.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q24" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="R24" t="n">
         <v>6.0</v>
       </c>
-      <c r="R24" t="n">
-        <v>5.0</v>
-      </c>
       <c r="S24" t="n">
         <v>0.0</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="25">
@@ -1870,7 +1870,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="K25" t="n">
         <v>1.0</v>
@@ -1882,10 +1882,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="O25" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="P25" t="n">
         <v>87.0</v>
@@ -2083,7 +2083,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" t="n">
-        <v>889.0</v>
+        <v>931.0</v>
       </c>
       <c r="K28" t="n">
         <v>1.0</v>
@@ -2095,13 +2095,13 @@
         <v>0.0</v>
       </c>
       <c r="N28" t="n">
-        <v>889.0</v>
+        <v>931.0</v>
       </c>
       <c r="O28" t="n">
-        <v>461.0</v>
+        <v>492.0</v>
       </c>
       <c r="P28" t="n">
-        <v>426.0</v>
+        <v>437.0</v>
       </c>
       <c r="Q28" t="n">
         <v>2.0</v>
@@ -2296,7 +2296,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" t="n">
-        <v>515.0</v>
+        <v>546.0</v>
       </c>
       <c r="K31" t="n">
         <v>1.0</v>
@@ -2308,13 +2308,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" t="n">
-        <v>515.0</v>
+        <v>546.0</v>
       </c>
       <c r="O31" t="n">
-        <v>245.0</v>
+        <v>261.0</v>
       </c>
       <c r="P31" t="n">
-        <v>265.0</v>
+        <v>280.0</v>
       </c>
       <c r="Q31" t="n">
         <v>5.0</v>
@@ -2367,7 +2367,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" t="n">
-        <v>628.0</v>
+        <v>655.0</v>
       </c>
       <c r="K32" t="n">
         <v>1.0</v>
@@ -2379,13 +2379,13 @@
         <v>0.0</v>
       </c>
       <c r="N32" t="n">
-        <v>628.0</v>
+        <v>655.0</v>
       </c>
       <c r="O32" t="n">
-        <v>294.0</v>
+        <v>310.0</v>
       </c>
       <c r="P32" t="n">
-        <v>317.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q32" t="n">
         <v>17.0</v>
@@ -2580,7 +2580,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" t="n">
-        <v>292.0</v>
+        <v>323.0</v>
       </c>
       <c r="K35" t="n">
         <v>1.0</v>
@@ -2592,13 +2592,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" t="n">
-        <v>292.0</v>
+        <v>323.0</v>
       </c>
       <c r="O35" t="n">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="P35" t="n">
-        <v>136.0</v>
+        <v>151.0</v>
       </c>
       <c r="Q35" t="n">
         <v>9.0</v>
@@ -2607,19 +2607,19 @@
         <v>0.0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="T35" t="n">
         <v>0.0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V35" t="n">
         <v>0.0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" t="n">
-        <v>455.0</v>
+        <v>463.0</v>
       </c>
       <c r="K36" t="n">
         <v>1.0</v>
@@ -2663,34 +2663,34 @@
         <v>0.0</v>
       </c>
       <c r="N36" t="n">
-        <v>455.0</v>
+        <v>463.0</v>
       </c>
       <c r="O36" t="n">
-        <v>188.0</v>
+        <v>193.0</v>
       </c>
       <c r="P36" t="n">
-        <v>267.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q36" t="n">
         <v>0.0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T36" t="n">
         <v>0.0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V36" t="n">
         <v>0.0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="37">
@@ -2722,7 +2722,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" t="n">
-        <v>400.0</v>
+        <v>416.0</v>
       </c>
       <c r="K37" t="n">
         <v>1.0</v>
@@ -2734,16 +2734,16 @@
         <v>0.0</v>
       </c>
       <c r="N37" t="n">
-        <v>400.0</v>
+        <v>416.0</v>
       </c>
       <c r="O37" t="n">
-        <v>209.0</v>
+        <v>217.0</v>
       </c>
       <c r="P37" t="n">
-        <v>189.0</v>
+        <v>195.0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R37" t="n">
         <v>0.0</v>
@@ -2793,7 +2793,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" t="n">
-        <v>843.0</v>
+        <v>886.0</v>
       </c>
       <c r="K38" t="n">
         <v>1.0</v>
@@ -2805,13 +2805,13 @@
         <v>0.0</v>
       </c>
       <c r="N38" t="n">
-        <v>843.0</v>
+        <v>886.0</v>
       </c>
       <c r="O38" t="n">
-        <v>475.0</v>
+        <v>513.0</v>
       </c>
       <c r="P38" t="n">
-        <v>368.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q38" t="n">
         <v>0.0</v>
@@ -3006,7 +3006,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" t="n">
-        <v>690.0</v>
+        <v>783.0</v>
       </c>
       <c r="K41" t="n">
         <v>1.0</v>
@@ -3018,10 +3018,10 @@
         <v>0.0</v>
       </c>
       <c r="N41" t="n">
-        <v>690.0</v>
+        <v>783.0</v>
       </c>
       <c r="O41" t="n">
-        <v>251.0</v>
+        <v>344.0</v>
       </c>
       <c r="P41" t="n">
         <v>439.0</v>
@@ -3148,7 +3148,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" t="n">
-        <v>631.0</v>
+        <v>671.0</v>
       </c>
       <c r="K43" t="n">
         <v>1.0</v>
@@ -3160,13 +3160,13 @@
         <v>0.0</v>
       </c>
       <c r="N43" t="n">
-        <v>631.0</v>
+        <v>671.0</v>
       </c>
       <c r="O43" t="n">
-        <v>294.0</v>
+        <v>322.0</v>
       </c>
       <c r="P43" t="n">
-        <v>337.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q43" t="n">
         <v>0.0</v>
@@ -3290,7 +3290,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" t="n">
-        <v>936.0</v>
+        <v>947.0</v>
       </c>
       <c r="K45" t="n">
         <v>1.0</v>
@@ -3302,10 +3302,10 @@
         <v>1.0</v>
       </c>
       <c r="N45" t="n">
-        <v>935.0</v>
+        <v>946.0</v>
       </c>
       <c r="O45" t="n">
-        <v>426.0</v>
+        <v>437.0</v>
       </c>
       <c r="P45" t="n">
         <v>508.0</v>
@@ -3361,7 +3361,7 @@
         <v>1429.0</v>
       </c>
       <c r="J46" t="n">
-        <v>1245.0</v>
+        <v>1304.0</v>
       </c>
       <c r="K46" t="n">
         <v>1.0</v>
@@ -3373,19 +3373,19 @@
         <v>0.0</v>
       </c>
       <c r="N46" t="n">
-        <v>1245.0</v>
+        <v>1304.0</v>
       </c>
       <c r="O46" t="n">
-        <v>647.0</v>
+        <v>674.0</v>
       </c>
       <c r="P46" t="n">
-        <v>587.0</v>
+        <v>602.0</v>
       </c>
       <c r="Q46" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="R46" t="n">
         <v>11.0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>8.0</v>
       </c>
       <c r="S46" t="n">
         <v>12.0</v>
@@ -3400,7 +3400,7 @@
         <v>0.0</v>
       </c>
       <c r="W46" t="n">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="47">
@@ -3432,7 +3432,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" t="n">
-        <v>704.0</v>
+        <v>719.0</v>
       </c>
       <c r="K47" t="n">
         <v>1.0</v>
@@ -3444,13 +3444,13 @@
         <v>0.0</v>
       </c>
       <c r="N47" t="n">
-        <v>704.0</v>
+        <v>719.0</v>
       </c>
       <c r="O47" t="n">
-        <v>385.0</v>
+        <v>393.0</v>
       </c>
       <c r="P47" t="n">
-        <v>318.0</v>
+        <v>325.0</v>
       </c>
       <c r="Q47" t="n">
         <v>1.0</v>
@@ -3503,7 +3503,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" t="n">
-        <v>785.0</v>
+        <v>815.0</v>
       </c>
       <c r="K48" t="n">
         <v>1.0</v>
@@ -3515,13 +3515,13 @@
         <v>0.0</v>
       </c>
       <c r="N48" t="n">
-        <v>785.0</v>
+        <v>815.0</v>
       </c>
       <c r="O48" t="n">
-        <v>431.0</v>
+        <v>441.0</v>
       </c>
       <c r="P48" t="n">
-        <v>354.0</v>
+        <v>374.0</v>
       </c>
       <c r="Q48" t="n">
         <v>0.0</v>
@@ -3574,7 +3574,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" t="n">
-        <v>858.0</v>
+        <v>904.0</v>
       </c>
       <c r="K49" t="n">
         <v>1.0</v>
@@ -3586,19 +3586,19 @@
         <v>0.0</v>
       </c>
       <c r="N49" t="n">
-        <v>858.0</v>
+        <v>904.0</v>
       </c>
       <c r="O49" t="n">
-        <v>430.0</v>
+        <v>471.0</v>
       </c>
       <c r="P49" t="n">
-        <v>428.0</v>
+        <v>433.0</v>
       </c>
       <c r="Q49" t="n">
         <v>0.0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S49" t="n">
         <v>0.0</v>
@@ -3613,7 +3613,7 @@
         <v>0.0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="50">
@@ -3858,7 +3858,7 @@
         <v>834.0</v>
       </c>
       <c r="J53" t="n">
-        <v>755.0</v>
+        <v>773.0</v>
       </c>
       <c r="K53" t="n">
         <v>1.0</v>
@@ -3870,13 +3870,13 @@
         <v>0.0</v>
       </c>
       <c r="N53" t="n">
-        <v>755.0</v>
+        <v>773.0</v>
       </c>
       <c r="O53" t="n">
-        <v>428.0</v>
+        <v>432.0</v>
       </c>
       <c r="P53" t="n">
-        <v>327.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q53" t="n">
         <v>0.0</v>
@@ -3888,7 +3888,7 @@
         <v>2.0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U53" t="n">
         <v>0.0</v>
@@ -3897,7 +3897,7 @@
         <v>0.0</v>
       </c>
       <c r="W53" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="54">
@@ -4000,7 +4000,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" t="n">
-        <v>286.0</v>
+        <v>350.0</v>
       </c>
       <c r="K55" t="n">
         <v>1.0</v>
@@ -4012,13 +4012,13 @@
         <v>0.0</v>
       </c>
       <c r="N55" t="n">
-        <v>286.0</v>
+        <v>350.0</v>
       </c>
       <c r="O55" t="n">
-        <v>128.0</v>
+        <v>149.0</v>
       </c>
       <c r="P55" t="n">
-        <v>158.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q55" t="n">
         <v>0.0</v>
@@ -4071,7 +4071,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" t="n">
-        <v>480.0</v>
+        <v>495.0</v>
       </c>
       <c r="K56" t="n">
         <v>1.0</v>
@@ -4083,13 +4083,13 @@
         <v>0.0</v>
       </c>
       <c r="N56" t="n">
-        <v>480.0</v>
+        <v>495.0</v>
       </c>
       <c r="O56" t="n">
-        <v>214.0</v>
+        <v>218.0</v>
       </c>
       <c r="P56" t="n">
-        <v>266.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q56" t="n">
         <v>0.0</v>
@@ -4142,7 +4142,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" t="n">
-        <v>403.0</v>
+        <v>435.0</v>
       </c>
       <c r="K57" t="n">
         <v>1.0</v>
@@ -4154,10 +4154,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" t="n">
-        <v>403.0</v>
+        <v>435.0</v>
       </c>
       <c r="O57" t="n">
-        <v>403.0</v>
+        <v>435.0</v>
       </c>
       <c r="P57" t="n">
         <v>0.0</v>
@@ -4213,7 +4213,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" t="n">
-        <v>583.0</v>
+        <v>631.0</v>
       </c>
       <c r="K58" t="n">
         <v>1.0</v>
@@ -4225,13 +4225,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" t="n">
-        <v>583.0</v>
+        <v>631.0</v>
       </c>
       <c r="O58" t="n">
-        <v>270.0</v>
+        <v>292.0</v>
       </c>
       <c r="P58" t="n">
-        <v>313.0</v>
+        <v>339.0</v>
       </c>
       <c r="Q58" t="n">
         <v>0.0</v>
@@ -4355,7 +4355,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" t="n">
-        <v>514.0</v>
+        <v>574.0</v>
       </c>
       <c r="K60" t="n">
         <v>1.0</v>
@@ -4367,13 +4367,13 @@
         <v>0.0</v>
       </c>
       <c r="N60" t="n">
-        <v>514.0</v>
+        <v>574.0</v>
       </c>
       <c r="O60" t="n">
-        <v>219.0</v>
+        <v>243.0</v>
       </c>
       <c r="P60" t="n">
-        <v>295.0</v>
+        <v>331.0</v>
       </c>
       <c r="Q60" t="n">
         <v>0.0</v>
@@ -4497,7 +4497,7 @@
         <v>570.0</v>
       </c>
       <c r="J62" t="n">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="K62" t="n">
         <v>1.0</v>
@@ -4509,13 +4509,13 @@
         <v>0.0</v>
       </c>
       <c r="N62" t="n">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="O62" t="n">
-        <v>253.0</v>
+        <v>263.0</v>
       </c>
       <c r="P62" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="Q62" t="n">
         <v>0.0</v>
@@ -4639,7 +4639,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" t="n">
-        <v>1013.0</v>
+        <v>1019.0</v>
       </c>
       <c r="K64" t="n">
         <v>1.0</v>
@@ -4651,19 +4651,19 @@
         <v>0.0</v>
       </c>
       <c r="N64" t="n">
-        <v>1013.0</v>
+        <v>1019.0</v>
       </c>
       <c r="O64" t="n">
-        <v>563.0</v>
+        <v>567.0</v>
       </c>
       <c r="P64" t="n">
-        <v>450.0</v>
+        <v>452.0</v>
       </c>
       <c r="Q64" t="n">
         <v>0.0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="S64" t="n">
         <v>0.0</v>
@@ -4678,7 +4678,7 @@
         <v>0.0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="65">
@@ -4781,7 +4781,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" t="n">
-        <v>993.0</v>
+        <v>997.0</v>
       </c>
       <c r="K66" t="n">
         <v>1.0</v>
@@ -4793,13 +4793,13 @@
         <v>0.0</v>
       </c>
       <c r="N66" t="n">
-        <v>993.0</v>
+        <v>997.0</v>
       </c>
       <c r="O66" t="n">
-        <v>538.0</v>
+        <v>541.0</v>
       </c>
       <c r="P66" t="n">
-        <v>455.0</v>
+        <v>456.0</v>
       </c>
       <c r="Q66" t="n">
         <v>0.0</v>
@@ -4808,7 +4808,7 @@
         <v>0.0</v>
       </c>
       <c r="S66" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T66" t="n">
         <v>0.0</v>
@@ -4820,7 +4820,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="67">
@@ -4994,7 +4994,7 @@
         <v>1121.0</v>
       </c>
       <c r="J69" t="n">
-        <v>901.0</v>
+        <v>910.0</v>
       </c>
       <c r="K69" t="n">
         <v>1.0</v>
@@ -5006,10 +5006,10 @@
         <v>1.0</v>
       </c>
       <c r="N69" t="n">
-        <v>900.0</v>
+        <v>909.0</v>
       </c>
       <c r="O69" t="n">
-        <v>451.0</v>
+        <v>460.0</v>
       </c>
       <c r="P69" t="n">
         <v>450.0</v>
@@ -5065,7 +5065,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" t="n">
-        <v>911.0</v>
+        <v>952.0</v>
       </c>
       <c r="K70" t="n">
         <v>1.0</v>
@@ -5077,16 +5077,16 @@
         <v>0.0</v>
       </c>
       <c r="N70" t="n">
-        <v>911.0</v>
+        <v>952.0</v>
       </c>
       <c r="O70" t="n">
-        <v>570.0</v>
+        <v>586.0</v>
       </c>
       <c r="P70" t="n">
-        <v>335.0</v>
+        <v>359.0</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="R70" t="n">
         <v>9.0</v>
@@ -5207,7 +5207,7 @@
         <v>1141.0</v>
       </c>
       <c r="J72" t="n">
-        <v>985.0</v>
+        <v>1028.0</v>
       </c>
       <c r="K72" t="n">
         <v>1.0</v>
@@ -5219,13 +5219,13 @@
         <v>0.0</v>
       </c>
       <c r="N72" t="n">
-        <v>985.0</v>
+        <v>1028.0</v>
       </c>
       <c r="O72" t="n">
-        <v>593.0</v>
+        <v>633.0</v>
       </c>
       <c r="P72" t="n">
-        <v>389.0</v>
+        <v>392.0</v>
       </c>
       <c r="Q72" t="n">
         <v>3.0</v>
@@ -5420,7 +5420,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" t="n">
-        <v>753.0</v>
+        <v>780.0</v>
       </c>
       <c r="K75" t="n">
         <v>1.0</v>
@@ -5432,13 +5432,13 @@
         <v>0.0</v>
       </c>
       <c r="N75" t="n">
-        <v>753.0</v>
+        <v>780.0</v>
       </c>
       <c r="O75" t="n">
-        <v>384.0</v>
+        <v>406.0</v>
       </c>
       <c r="P75" t="n">
-        <v>368.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q75" t="n">
         <v>1.0</v>
@@ -5491,7 +5491,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" t="n">
-        <v>733.0</v>
+        <v>739.0</v>
       </c>
       <c r="K76" t="n">
         <v>1.0</v>
@@ -5503,13 +5503,13 @@
         <v>0.0</v>
       </c>
       <c r="N76" t="n">
-        <v>733.0</v>
+        <v>739.0</v>
       </c>
       <c r="O76" t="n">
-        <v>386.0</v>
+        <v>390.0</v>
       </c>
       <c r="P76" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q76" t="n">
         <v>0.0</v>
@@ -5633,7 +5633,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" t="n">
-        <v>327.0</v>
+        <v>367.0</v>
       </c>
       <c r="K78" t="n">
         <v>1.0</v>
@@ -5645,13 +5645,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" t="n">
-        <v>327.0</v>
+        <v>367.0</v>
       </c>
       <c r="O78" t="n">
-        <v>88.0</v>
+        <v>115.0</v>
       </c>
       <c r="P78" t="n">
-        <v>239.0</v>
+        <v>252.0</v>
       </c>
       <c r="Q78" t="n">
         <v>0.0</v>
@@ -5704,7 +5704,7 @@
         <v>786.0</v>
       </c>
       <c r="J79" t="n">
-        <v>245.0</v>
+        <v>275.0</v>
       </c>
       <c r="K79" t="n">
         <v>1.0</v>
@@ -5716,13 +5716,13 @@
         <v>0.0</v>
       </c>
       <c r="N79" t="n">
-        <v>245.0</v>
+        <v>275.0</v>
       </c>
       <c r="O79" t="n">
-        <v>38.0</v>
+        <v>65.0</v>
       </c>
       <c r="P79" t="n">
-        <v>207.0</v>
+        <v>210.0</v>
       </c>
       <c r="Q79" t="n">
         <v>0.0</v>
@@ -5775,7 +5775,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" t="n">
-        <v>768.0</v>
+        <v>799.0</v>
       </c>
       <c r="K80" t="n">
         <v>1.0</v>
@@ -5787,13 +5787,13 @@
         <v>0.0</v>
       </c>
       <c r="N80" t="n">
-        <v>768.0</v>
+        <v>799.0</v>
       </c>
       <c r="O80" t="n">
-        <v>420.0</v>
+        <v>436.0</v>
       </c>
       <c r="P80" t="n">
-        <v>348.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q80" t="n">
         <v>0.0</v>
@@ -5846,7 +5846,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" t="n">
-        <v>619.0</v>
+        <v>658.0</v>
       </c>
       <c r="K81" t="n">
         <v>1.0</v>
@@ -5858,13 +5858,13 @@
         <v>0.0</v>
       </c>
       <c r="N81" t="n">
-        <v>619.0</v>
+        <v>658.0</v>
       </c>
       <c r="O81" t="n">
-        <v>307.0</v>
+        <v>341.0</v>
       </c>
       <c r="P81" t="n">
-        <v>312.0</v>
+        <v>317.0</v>
       </c>
       <c r="Q81" t="n">
         <v>0.0</v>
@@ -5873,10 +5873,10 @@
         <v>7.0</v>
       </c>
       <c r="S81" t="n">
-        <v>13.0</v>
+        <v>19.0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U81" t="n">
         <v>0.0</v>
@@ -5885,7 +5885,7 @@
         <v>0.0</v>
       </c>
       <c r="W81" t="n">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="82">
@@ -5917,7 +5917,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" t="n">
-        <v>745.0</v>
+        <v>800.0</v>
       </c>
       <c r="K82" t="n">
         <v>1.0</v>
@@ -5929,13 +5929,13 @@
         <v>0.0</v>
       </c>
       <c r="N82" t="n">
-        <v>745.0</v>
+        <v>800.0</v>
       </c>
       <c r="O82" t="n">
-        <v>314.0</v>
+        <v>368.0</v>
       </c>
       <c r="P82" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q82" t="n">
         <v>0.0</v>
@@ -5988,7 +5988,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" t="n">
-        <v>650.0</v>
+        <v>680.0</v>
       </c>
       <c r="K83" t="n">
         <v>1.0</v>
@@ -6000,13 +6000,13 @@
         <v>0.0</v>
       </c>
       <c r="N83" t="n">
-        <v>650.0</v>
+        <v>680.0</v>
       </c>
       <c r="O83" t="n">
-        <v>240.0</v>
+        <v>269.0</v>
       </c>
       <c r="P83" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q83" t="n">
         <v>0.0</v>
@@ -6059,7 +6059,7 @@
         <v>451.0</v>
       </c>
       <c r="J84" t="n">
-        <v>320.0</v>
+        <v>332.0</v>
       </c>
       <c r="K84" t="n">
         <v>1.0</v>
@@ -6071,10 +6071,10 @@
         <v>0.0</v>
       </c>
       <c r="N84" t="n">
-        <v>320.0</v>
+        <v>332.0</v>
       </c>
       <c r="O84" t="n">
-        <v>127.0</v>
+        <v>139.0</v>
       </c>
       <c r="P84" t="n">
         <v>193.0</v>
@@ -6130,7 +6130,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" t="n">
-        <v>946.0</v>
+        <v>962.0</v>
       </c>
       <c r="K85" t="n">
         <v>1.0</v>
@@ -6142,13 +6142,13 @@
         <v>0.0</v>
       </c>
       <c r="N85" t="n">
-        <v>946.0</v>
+        <v>962.0</v>
       </c>
       <c r="O85" t="n">
-        <v>440.0</v>
+        <v>447.0</v>
       </c>
       <c r="P85" t="n">
-        <v>506.0</v>
+        <v>515.0</v>
       </c>
       <c r="Q85" t="n">
         <v>0.0</v>
@@ -6201,7 +6201,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" t="n">
-        <v>726.0</v>
+        <v>766.0</v>
       </c>
       <c r="K86" t="n">
         <v>1.0</v>
@@ -6213,13 +6213,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" t="n">
-        <v>726.0</v>
+        <v>766.0</v>
       </c>
       <c r="O86" t="n">
-        <v>331.0</v>
+        <v>358.0</v>
       </c>
       <c r="P86" t="n">
-        <v>395.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q86" t="n">
         <v>0.0</v>
@@ -6272,7 +6272,7 @@
         <v>735.0</v>
       </c>
       <c r="J87" t="n">
-        <v>615.0</v>
+        <v>629.0</v>
       </c>
       <c r="K87" t="n">
         <v>1.0</v>
@@ -6284,34 +6284,34 @@
         <v>0.0</v>
       </c>
       <c r="N87" t="n">
-        <v>615.0</v>
+        <v>629.0</v>
       </c>
       <c r="O87" t="n">
-        <v>311.0</v>
+        <v>319.0</v>
       </c>
       <c r="P87" t="n">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="Q87" t="n">
         <v>0.0</v>
       </c>
       <c r="R87" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="S87" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T87" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="U87" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V87" t="n">
         <v>0.0</v>
       </c>
       <c r="W87" t="n">
-        <v>17.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="88">
@@ -6343,7 +6343,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" t="n">
-        <v>500.0</v>
+        <v>590.0</v>
       </c>
       <c r="K88" t="n">
         <v>1.0</v>
@@ -6355,13 +6355,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" t="n">
-        <v>500.0</v>
+        <v>590.0</v>
       </c>
       <c r="O88" t="n">
-        <v>230.0</v>
+        <v>274.0</v>
       </c>
       <c r="P88" t="n">
-        <v>270.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q88" t="n">
         <v>0.0</v>
@@ -6485,7 +6485,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" t="n">
-        <v>598.0</v>
+        <v>637.0</v>
       </c>
       <c r="K90" t="n">
         <v>1.0</v>
@@ -6497,13 +6497,13 @@
         <v>0.0</v>
       </c>
       <c r="N90" t="n">
-        <v>598.0</v>
+        <v>637.0</v>
       </c>
       <c r="O90" t="n">
-        <v>288.0</v>
+        <v>322.0</v>
       </c>
       <c r="P90" t="n">
-        <v>309.0</v>
+        <v>314.0</v>
       </c>
       <c r="Q90" t="n">
         <v>1.0</v>
@@ -6512,10 +6512,10 @@
         <v>14.0</v>
       </c>
       <c r="S90" t="n">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
       <c r="T90" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U90" t="n">
         <v>0.0</v>
@@ -6524,7 +6524,7 @@
         <v>0.0</v>
       </c>
       <c r="W90" t="n">
-        <v>77.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="91">
@@ -6556,7 +6556,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" t="n">
-        <v>463.0</v>
+        <v>532.0</v>
       </c>
       <c r="K91" t="n">
         <v>1.0</v>
@@ -6568,34 +6568,34 @@
         <v>0.0</v>
       </c>
       <c r="N91" t="n">
-        <v>463.0</v>
+        <v>532.0</v>
       </c>
       <c r="O91" t="n">
-        <v>50.0</v>
+        <v>82.0</v>
       </c>
       <c r="P91" t="n">
-        <v>284.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q91" t="n">
-        <v>129.0</v>
+        <v>143.0</v>
       </c>
       <c r="R91" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="S91" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="T91" t="n">
         <v>0.0</v>
       </c>
       <c r="U91" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="V91" t="n">
         <v>0.0</v>
       </c>
       <c r="W91" t="n">
-        <v>51.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="92">
@@ -6722,7 +6722,7 @@
         <v>1.0</v>
       </c>
       <c r="R93" t="n">
-        <v>11.0</v>
+        <v>25.0</v>
       </c>
       <c r="S93" t="n">
         <v>1.0</v>
@@ -6734,10 +6734,10 @@
         <v>0.0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W93" t="n">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="94">
@@ -6769,7 +6769,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" t="n">
-        <v>472.0</v>
+        <v>506.0</v>
       </c>
       <c r="K94" t="n">
         <v>1.0</v>
@@ -6781,13 +6781,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" t="n">
-        <v>472.0</v>
+        <v>506.0</v>
       </c>
       <c r="O94" t="n">
-        <v>206.0</v>
+        <v>218.0</v>
       </c>
       <c r="P94" t="n">
-        <v>266.0</v>
+        <v>288.0</v>
       </c>
       <c r="Q94" t="n">
         <v>0.0</v>
@@ -6796,7 +6796,7 @@
         <v>0.0</v>
       </c>
       <c r="S94" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T94" t="n">
         <v>0.0</v>
@@ -6808,7 +6808,7 @@
         <v>0.0</v>
       </c>
       <c r="W94" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="95">
@@ -6840,7 +6840,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" t="n">
-        <v>1096.0</v>
+        <v>1166.0</v>
       </c>
       <c r="K95" t="n">
         <v>1.0</v>
@@ -6852,13 +6852,13 @@
         <v>0.0</v>
       </c>
       <c r="N95" t="n">
-        <v>1096.0</v>
+        <v>1166.0</v>
       </c>
       <c r="O95" t="n">
-        <v>469.0</v>
+        <v>523.0</v>
       </c>
       <c r="P95" t="n">
-        <v>627.0</v>
+        <v>643.0</v>
       </c>
       <c r="Q95" t="n">
         <v>0.0</v>
@@ -6911,7 +6911,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" t="n">
-        <v>567.0</v>
+        <v>604.0</v>
       </c>
       <c r="K96" t="n">
         <v>1.0</v>
@@ -6923,19 +6923,19 @@
         <v>0.0</v>
       </c>
       <c r="N96" t="n">
-        <v>567.0</v>
+        <v>604.0</v>
       </c>
       <c r="O96" t="n">
-        <v>244.0</v>
+        <v>274.0</v>
       </c>
       <c r="P96" t="n">
-        <v>323.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q96" t="n">
         <v>0.0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S96" t="n">
         <v>0.0</v>
@@ -6950,7 +6950,7 @@
         <v>0.0</v>
       </c>
       <c r="W96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="97">
@@ -6982,7 +6982,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" t="n">
-        <v>498.0</v>
+        <v>575.0</v>
       </c>
       <c r="K97" t="n">
         <v>1.0</v>
@@ -6994,13 +6994,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" t="n">
-        <v>498.0</v>
+        <v>575.0</v>
       </c>
       <c r="O97" t="n">
-        <v>238.0</v>
+        <v>282.0</v>
       </c>
       <c r="P97" t="n">
-        <v>260.0</v>
+        <v>293.0</v>
       </c>
       <c r="Q97" t="n">
         <v>0.0</v>
@@ -7053,7 +7053,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" t="n">
-        <v>279.0</v>
+        <v>306.0</v>
       </c>
       <c r="K98" t="n">
         <v>1.0</v>
@@ -7065,19 +7065,19 @@
         <v>0.0</v>
       </c>
       <c r="N98" t="n">
-        <v>279.0</v>
+        <v>306.0</v>
       </c>
       <c r="O98" t="n">
-        <v>115.0</v>
+        <v>128.0</v>
       </c>
       <c r="P98" t="n">
-        <v>164.0</v>
+        <v>178.0</v>
       </c>
       <c r="Q98" t="n">
         <v>0.0</v>
       </c>
       <c r="R98" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="S98" t="n">
         <v>0.0</v>
@@ -7092,7 +7092,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="99">
@@ -7124,7 +7124,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" t="n">
-        <v>584.0</v>
+        <v>646.0</v>
       </c>
       <c r="K99" t="n">
         <v>1.0</v>
@@ -7136,13 +7136,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" t="n">
-        <v>584.0</v>
+        <v>646.0</v>
       </c>
       <c r="O99" t="n">
-        <v>265.0</v>
+        <v>325.0</v>
       </c>
       <c r="P99" t="n">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q99" t="n">
         <v>0.0</v>
@@ -7266,7 +7266,7 @@
         <v>1059.0</v>
       </c>
       <c r="J101" t="n">
-        <v>913.0</v>
+        <v>924.0</v>
       </c>
       <c r="K101" t="n">
         <v>1.0</v>
@@ -7278,10 +7278,10 @@
         <v>0.0</v>
       </c>
       <c r="N101" t="n">
-        <v>913.0</v>
+        <v>924.0</v>
       </c>
       <c r="O101" t="n">
-        <v>469.0</v>
+        <v>480.0</v>
       </c>
       <c r="P101" t="n">
         <v>444.0</v>
@@ -7337,7 +7337,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" t="n">
-        <v>710.0</v>
+        <v>716.0</v>
       </c>
       <c r="K102" t="n">
         <v>1.0</v>
@@ -7349,13 +7349,13 @@
         <v>0.0</v>
       </c>
       <c r="N102" t="n">
-        <v>710.0</v>
+        <v>716.0</v>
       </c>
       <c r="O102" t="n">
-        <v>326.0</v>
+        <v>329.0</v>
       </c>
       <c r="P102" t="n">
-        <v>384.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q102" t="n">
         <v>0.0</v>
@@ -7364,7 +7364,7 @@
         <v>32.0</v>
       </c>
       <c r="S102" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="T102" t="n">
         <v>0.0</v>
@@ -7376,7 +7376,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="103">
@@ -7408,7 +7408,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" t="n">
-        <v>376.0</v>
+        <v>395.0</v>
       </c>
       <c r="K103" t="n">
         <v>1.0</v>
@@ -7420,10 +7420,10 @@
         <v>0.0</v>
       </c>
       <c r="N103" t="n">
-        <v>376.0</v>
+        <v>395.0</v>
       </c>
       <c r="O103" t="n">
-        <v>167.0</v>
+        <v>186.0</v>
       </c>
       <c r="P103" t="n">
         <v>209.0</v>
@@ -7479,7 +7479,7 @@
         <v>821.0</v>
       </c>
       <c r="J104" t="n">
-        <v>727.0</v>
+        <v>734.0</v>
       </c>
       <c r="K104" t="n">
         <v>1.0</v>
@@ -7491,22 +7491,22 @@
         <v>0.0</v>
       </c>
       <c r="N104" t="n">
-        <v>727.0</v>
+        <v>734.0</v>
       </c>
       <c r="O104" t="n">
-        <v>337.0</v>
+        <v>339.0</v>
       </c>
       <c r="P104" t="n">
-        <v>390.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q104" t="n">
         <v>0.0</v>
       </c>
       <c r="R104" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="S104" t="n">
-        <v>51.0</v>
+        <v>76.0</v>
       </c>
       <c r="T104" t="n">
         <v>1.0</v>
@@ -7518,7 +7518,7 @@
         <v>0.0</v>
       </c>
       <c r="W104" t="n">
-        <v>57.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="105">
@@ -7550,7 +7550,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" t="n">
-        <v>598.0</v>
+        <v>630.0</v>
       </c>
       <c r="K105" t="n">
         <v>1.0</v>
@@ -7562,22 +7562,22 @@
         <v>0.0</v>
       </c>
       <c r="N105" t="n">
-        <v>598.0</v>
+        <v>630.0</v>
       </c>
       <c r="O105" t="n">
-        <v>256.0</v>
+        <v>283.0</v>
       </c>
       <c r="P105" t="n">
-        <v>342.0</v>
+        <v>347.0</v>
       </c>
       <c r="Q105" t="n">
         <v>0.0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.0</v>
+        <v>34.0</v>
       </c>
       <c r="S105" t="n">
-        <v>30.0</v>
+        <v>64.0</v>
       </c>
       <c r="T105" t="n">
         <v>0.0</v>
@@ -7589,7 +7589,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" t="n">
-        <v>33.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="106">
@@ -7621,7 +7621,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" t="n">
-        <v>686.0</v>
+        <v>701.0</v>
       </c>
       <c r="K106" t="n">
         <v>1.0</v>
@@ -7633,16 +7633,16 @@
         <v>0.0</v>
       </c>
       <c r="N106" t="n">
-        <v>686.0</v>
+        <v>701.0</v>
       </c>
       <c r="O106" t="n">
-        <v>279.0</v>
+        <v>293.0</v>
       </c>
       <c r="P106" t="n">
         <v>398.0</v>
       </c>
       <c r="Q106" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R106" t="n">
         <v>0.0</v>
@@ -7692,7 +7692,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" t="n">
-        <v>382.0</v>
+        <v>405.0</v>
       </c>
       <c r="K107" t="n">
         <v>1.0</v>
@@ -7704,13 +7704,13 @@
         <v>2.0</v>
       </c>
       <c r="N107" t="n">
-        <v>380.0</v>
+        <v>403.0</v>
       </c>
       <c r="O107" t="n">
-        <v>159.0</v>
+        <v>174.0</v>
       </c>
       <c r="P107" t="n">
-        <v>223.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q107" t="n">
         <v>0.0</v>
@@ -7763,7 +7763,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" t="n">
-        <v>407.0</v>
+        <v>432.0</v>
       </c>
       <c r="K108" t="n">
         <v>1.0</v>
@@ -7775,13 +7775,13 @@
         <v>0.0</v>
       </c>
       <c r="N108" t="n">
-        <v>407.0</v>
+        <v>432.0</v>
       </c>
       <c r="O108" t="n">
-        <v>219.0</v>
+        <v>235.0</v>
       </c>
       <c r="P108" t="n">
-        <v>188.0</v>
+        <v>197.0</v>
       </c>
       <c r="Q108" t="n">
         <v>0.0</v>
@@ -7834,7 +7834,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" t="n">
-        <v>521.0</v>
+        <v>555.0</v>
       </c>
       <c r="K109" t="n">
         <v>1.0</v>
@@ -7846,13 +7846,13 @@
         <v>0.0</v>
       </c>
       <c r="N109" t="n">
-        <v>521.0</v>
+        <v>555.0</v>
       </c>
       <c r="O109" t="n">
-        <v>272.0</v>
+        <v>286.0</v>
       </c>
       <c r="P109" t="n">
-        <v>249.0</v>
+        <v>269.0</v>
       </c>
       <c r="Q109" t="n">
         <v>0.0</v>
@@ -7861,7 +7861,7 @@
         <v>28.0</v>
       </c>
       <c r="S109" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="T109" t="n">
         <v>1.0</v>
@@ -7873,7 +7873,7 @@
         <v>0.0</v>
       </c>
       <c r="W109" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="110">
@@ -7905,7 +7905,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" t="n">
-        <v>368.0</v>
+        <v>387.0</v>
       </c>
       <c r="K110" t="n">
         <v>1.0</v>
@@ -7917,19 +7917,19 @@
         <v>0.0</v>
       </c>
       <c r="N110" t="n">
-        <v>368.0</v>
+        <v>387.0</v>
       </c>
       <c r="O110" t="n">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="P110" t="n">
-        <v>206.0</v>
+        <v>218.0</v>
       </c>
       <c r="Q110" t="n">
         <v>0.0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S110" t="n">
         <v>6.0</v>
@@ -7944,7 +7944,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="111">
@@ -7976,7 +7976,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" t="n">
-        <v>669.0</v>
+        <v>701.0</v>
       </c>
       <c r="K111" t="n">
         <v>1.0</v>
@@ -7988,13 +7988,13 @@
         <v>0.0</v>
       </c>
       <c r="N111" t="n">
-        <v>669.0</v>
+        <v>701.0</v>
       </c>
       <c r="O111" t="n">
-        <v>269.0</v>
+        <v>297.0</v>
       </c>
       <c r="P111" t="n">
-        <v>400.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q111" t="n">
         <v>0.0</v>
@@ -8003,7 +8003,7 @@
         <v>5.0</v>
       </c>
       <c r="S111" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T111" t="n">
         <v>0.0</v>
@@ -8015,7 +8015,7 @@
         <v>0.0</v>
       </c>
       <c r="W111" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="112">
@@ -8047,7 +8047,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" t="n">
-        <v>397.0</v>
+        <v>413.0</v>
       </c>
       <c r="K112" t="n">
         <v>1.0</v>
@@ -8059,22 +8059,22 @@
         <v>0.0</v>
       </c>
       <c r="N112" t="n">
-        <v>397.0</v>
+        <v>413.0</v>
       </c>
       <c r="O112" t="n">
-        <v>190.0</v>
+        <v>200.0</v>
       </c>
       <c r="P112" t="n">
-        <v>206.0</v>
+        <v>209.0</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="R112" t="n">
         <v>9.0</v>
       </c>
       <c r="S112" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="T112" t="n">
         <v>0.0</v>
@@ -8086,7 +8086,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" t="n">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="113">
@@ -8118,7 +8118,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" t="n">
-        <v>452.0</v>
+        <v>472.0</v>
       </c>
       <c r="K113" t="n">
         <v>1.0</v>
@@ -8130,13 +8130,13 @@
         <v>0.0</v>
       </c>
       <c r="N113" t="n">
-        <v>452.0</v>
+        <v>472.0</v>
       </c>
       <c r="O113" t="n">
-        <v>151.0</v>
+        <v>157.0</v>
       </c>
       <c r="P113" t="n">
-        <v>301.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q113" t="n">
         <v>0.0</v>
@@ -8189,7 +8189,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" t="n">
-        <v>465.0</v>
+        <v>479.0</v>
       </c>
       <c r="K114" t="n">
         <v>1.0</v>
@@ -8201,13 +8201,13 @@
         <v>0.0</v>
       </c>
       <c r="N114" t="n">
-        <v>465.0</v>
+        <v>479.0</v>
       </c>
       <c r="O114" t="n">
-        <v>231.0</v>
+        <v>238.0</v>
       </c>
       <c r="P114" t="n">
-        <v>233.0</v>
+        <v>240.0</v>
       </c>
       <c r="Q114" t="n">
         <v>1.0</v>
@@ -8260,7 +8260,7 @@
         <v>1337.0</v>
       </c>
       <c r="J115" t="n">
-        <v>869.0</v>
+        <v>978.0</v>
       </c>
       <c r="K115" t="n">
         <v>1.0</v>
@@ -8272,13 +8272,13 @@
         <v>0.0</v>
       </c>
       <c r="N115" t="n">
-        <v>869.0</v>
+        <v>978.0</v>
       </c>
       <c r="O115" t="n">
-        <v>362.0</v>
+        <v>438.0</v>
       </c>
       <c r="P115" t="n">
-        <v>507.0</v>
+        <v>540.0</v>
       </c>
       <c r="Q115" t="n">
         <v>0.0</v>
@@ -8331,7 +8331,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" t="n">
-        <v>404.0</v>
+        <v>422.0</v>
       </c>
       <c r="K116" t="n">
         <v>1.0</v>
@@ -8343,13 +8343,13 @@
         <v>1.0</v>
       </c>
       <c r="N116" t="n">
-        <v>403.0</v>
+        <v>421.0</v>
       </c>
       <c r="O116" t="n">
-        <v>55.0</v>
+        <v>63.0</v>
       </c>
       <c r="P116" t="n">
-        <v>185.0</v>
+        <v>195.0</v>
       </c>
       <c r="Q116" t="n">
         <v>164.0</v>
@@ -8402,7 +8402,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" t="n">
-        <v>405.0</v>
+        <v>416.0</v>
       </c>
       <c r="K117" t="n">
         <v>1.0</v>
@@ -8414,13 +8414,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" t="n">
-        <v>404.0</v>
+        <v>415.0</v>
       </c>
       <c r="O117" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="P117" t="n">
-        <v>221.0</v>
+        <v>230.0</v>
       </c>
       <c r="Q117" t="n">
         <v>0.0</v>
@@ -8473,7 +8473,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" t="n">
-        <v>466.0</v>
+        <v>488.0</v>
       </c>
       <c r="K118" t="n">
         <v>1.0</v>
@@ -8485,22 +8485,22 @@
         <v>0.0</v>
       </c>
       <c r="N118" t="n">
-        <v>466.0</v>
+        <v>488.0</v>
       </c>
       <c r="O118" t="n">
-        <v>238.0</v>
+        <v>252.0</v>
       </c>
       <c r="P118" t="n">
-        <v>226.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q118" t="n">
         <v>2.0</v>
       </c>
       <c r="R118" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S118" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T118" t="n">
         <v>1.0</v>
@@ -8512,7 +8512,7 @@
         <v>2.0</v>
       </c>
       <c r="W118" t="n">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="119">
@@ -8544,7 +8544,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" t="n">
-        <v>423.0</v>
+        <v>466.0</v>
       </c>
       <c r="K119" t="n">
         <v>1.0</v>
@@ -8556,19 +8556,19 @@
         <v>0.0</v>
       </c>
       <c r="N119" t="n">
-        <v>423.0</v>
+        <v>466.0</v>
       </c>
       <c r="O119" t="n">
-        <v>223.0</v>
+        <v>256.0</v>
       </c>
       <c r="P119" t="n">
-        <v>197.0</v>
+        <v>207.0</v>
       </c>
       <c r="Q119" t="n">
         <v>3.0</v>
       </c>
       <c r="R119" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="S119" t="n">
         <v>4.0</v>
@@ -8583,7 +8583,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="120">
@@ -8615,7 +8615,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" t="n">
-        <v>328.0</v>
+        <v>390.0</v>
       </c>
       <c r="K120" t="n">
         <v>1.0</v>
@@ -8627,19 +8627,19 @@
         <v>0.0</v>
       </c>
       <c r="N120" t="n">
-        <v>328.0</v>
+        <v>390.0</v>
       </c>
       <c r="O120" t="n">
-        <v>156.0</v>
+        <v>183.0</v>
       </c>
       <c r="P120" t="n">
-        <v>172.0</v>
+        <v>207.0</v>
       </c>
       <c r="Q120" t="n">
         <v>0.0</v>
       </c>
       <c r="R120" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="S120" t="n">
         <v>2.0</v>
@@ -8654,7 +8654,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="121">
@@ -8686,7 +8686,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" t="n">
-        <v>471.0</v>
+        <v>478.0</v>
       </c>
       <c r="K121" t="n">
         <v>1.0</v>
@@ -8698,19 +8698,19 @@
         <v>0.0</v>
       </c>
       <c r="N121" t="n">
-        <v>471.0</v>
+        <v>478.0</v>
       </c>
       <c r="O121" t="n">
-        <v>259.0</v>
+        <v>263.0</v>
       </c>
       <c r="P121" t="n">
-        <v>212.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q121" t="n">
         <v>0.0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S121" t="n">
         <v>0.0</v>
@@ -8725,7 +8725,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -8757,7 +8757,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" t="n">
-        <v>376.0</v>
+        <v>408.0</v>
       </c>
       <c r="K122" t="n">
         <v>1.0</v>
@@ -8769,13 +8769,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" t="n">
-        <v>372.0</v>
+        <v>404.0</v>
       </c>
       <c r="O122" t="n">
-        <v>182.0</v>
+        <v>206.0</v>
       </c>
       <c r="P122" t="n">
-        <v>179.0</v>
+        <v>187.0</v>
       </c>
       <c r="Q122" t="n">
         <v>15.0</v>
@@ -8899,7 +8899,7 @@
         <v>507.0</v>
       </c>
       <c r="J124" t="n">
-        <v>419.0</v>
+        <v>446.0</v>
       </c>
       <c r="K124" t="n">
         <v>1.0</v>
@@ -8911,19 +8911,19 @@
         <v>0.0</v>
       </c>
       <c r="N124" t="n">
-        <v>419.0</v>
+        <v>446.0</v>
       </c>
       <c r="O124" t="n">
-        <v>187.0</v>
+        <v>210.0</v>
       </c>
       <c r="P124" t="n">
-        <v>232.0</v>
+        <v>236.0</v>
       </c>
       <c r="Q124" t="n">
         <v>0.0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="S124" t="n">
         <v>0.0</v>
@@ -8938,7 +8938,7 @@
         <v>0.0</v>
       </c>
       <c r="W124" t="n">
-        <v>1.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="125">
@@ -8970,7 +8970,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" t="n">
-        <v>946.0</v>
+        <v>1005.0</v>
       </c>
       <c r="K125" t="n">
         <v>1.0</v>
@@ -8982,16 +8982,16 @@
         <v>0.0</v>
       </c>
       <c r="N125" t="n">
-        <v>946.0</v>
+        <v>1005.0</v>
       </c>
       <c r="O125" t="n">
-        <v>451.0</v>
+        <v>473.0</v>
       </c>
       <c r="P125" t="n">
-        <v>483.0</v>
+        <v>505.0</v>
       </c>
       <c r="Q125" t="n">
-        <v>12.0</v>
+        <v>27.0</v>
       </c>
       <c r="R125" t="n">
         <v>0.0</v>
@@ -9041,7 +9041,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" t="n">
-        <v>703.0</v>
+        <v>720.0</v>
       </c>
       <c r="K126" t="n">
         <v>1.0</v>
@@ -9053,13 +9053,13 @@
         <v>2.0</v>
       </c>
       <c r="N126" t="n">
-        <v>701.0</v>
+        <v>718.0</v>
       </c>
       <c r="O126" t="n">
-        <v>366.0</v>
+        <v>372.0</v>
       </c>
       <c r="P126" t="n">
-        <v>337.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q126" t="n">
         <v>0.0</v>
@@ -9112,7 +9112,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" t="n">
-        <v>653.0</v>
+        <v>697.0</v>
       </c>
       <c r="K127" t="n">
         <v>1.0</v>
@@ -9124,13 +9124,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" t="n">
-        <v>653.0</v>
+        <v>697.0</v>
       </c>
       <c r="O127" t="n">
-        <v>413.0</v>
+        <v>442.0</v>
       </c>
       <c r="P127" t="n">
-        <v>240.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q127" t="n">
         <v>0.0</v>
@@ -9183,7 +9183,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" t="n">
-        <v>697.0</v>
+        <v>752.0</v>
       </c>
       <c r="K128" t="n">
         <v>1.0</v>
@@ -9195,13 +9195,13 @@
         <v>0.0</v>
       </c>
       <c r="N128" t="n">
-        <v>697.0</v>
+        <v>752.0</v>
       </c>
       <c r="O128" t="n">
-        <v>354.0</v>
+        <v>386.0</v>
       </c>
       <c r="P128" t="n">
-        <v>342.0</v>
+        <v>365.0</v>
       </c>
       <c r="Q128" t="n">
         <v>1.0</v>
@@ -9210,7 +9210,7 @@
         <v>14.0</v>
       </c>
       <c r="S128" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T128" t="n">
         <v>0.0</v>
@@ -9222,7 +9222,7 @@
         <v>0.0</v>
       </c>
       <c r="W128" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="129">
@@ -9254,7 +9254,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" t="n">
-        <v>254.0</v>
+        <v>273.0</v>
       </c>
       <c r="K129" t="n">
         <v>1.0</v>
@@ -9266,13 +9266,13 @@
         <v>0.0</v>
       </c>
       <c r="N129" t="n">
-        <v>254.0</v>
+        <v>273.0</v>
       </c>
       <c r="O129" t="n">
-        <v>86.0</v>
+        <v>99.0</v>
       </c>
       <c r="P129" t="n">
-        <v>167.0</v>
+        <v>173.0</v>
       </c>
       <c r="Q129" t="n">
         <v>1.0</v>
@@ -9325,7 +9325,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" t="n">
-        <v>451.0</v>
+        <v>457.0</v>
       </c>
       <c r="K130" t="n">
         <v>1.0</v>
@@ -9337,13 +9337,13 @@
         <v>2.0</v>
       </c>
       <c r="N130" t="n">
-        <v>449.0</v>
+        <v>455.0</v>
       </c>
       <c r="O130" t="n">
-        <v>289.0</v>
+        <v>294.0</v>
       </c>
       <c r="P130" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="Q130" t="n">
         <v>18.0</v>
@@ -9396,7 +9396,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" t="n">
-        <v>432.0</v>
+        <v>434.0</v>
       </c>
       <c r="K131" t="n">
         <v>1.0</v>
@@ -9408,10 +9408,10 @@
         <v>5.0</v>
       </c>
       <c r="N131" t="n">
-        <v>427.0</v>
+        <v>429.0</v>
       </c>
       <c r="O131" t="n">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
       <c r="P131" t="n">
         <v>194.0</v>
@@ -9467,7 +9467,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" t="n">
-        <v>399.0</v>
+        <v>401.0</v>
       </c>
       <c r="K132" t="n">
         <v>1.0</v>
@@ -9479,13 +9479,13 @@
         <v>4.0</v>
       </c>
       <c r="N132" t="n">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="O132" t="n">
         <v>160.0</v>
       </c>
       <c r="P132" t="n">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q132" t="n">
         <v>7.0</v>
@@ -9538,7 +9538,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" t="n">
-        <v>447.0</v>
+        <v>550.0</v>
       </c>
       <c r="K133" t="n">
         <v>1.0</v>
@@ -9550,16 +9550,16 @@
         <v>0.0</v>
       </c>
       <c r="N133" t="n">
-        <v>447.0</v>
+        <v>550.0</v>
       </c>
       <c r="O133" t="n">
-        <v>229.0</v>
+        <v>278.0</v>
       </c>
       <c r="P133" t="n">
-        <v>209.0</v>
+        <v>261.0</v>
       </c>
       <c r="Q133" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="R133" t="n">
         <v>0.0</v>
@@ -9609,7 +9609,7 @@
         <v>1343.0</v>
       </c>
       <c r="J134" t="n">
-        <v>1066.0</v>
+        <v>1070.0</v>
       </c>
       <c r="K134" t="n">
         <v>1.0</v>
@@ -9621,16 +9621,16 @@
         <v>1.0</v>
       </c>
       <c r="N134" t="n">
-        <v>1065.0</v>
+        <v>1069.0</v>
       </c>
       <c r="O134" t="n">
-        <v>687.0</v>
+        <v>689.0</v>
       </c>
       <c r="P134" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R134" t="n">
         <v>0.0</v>
@@ -9680,7 +9680,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" t="n">
-        <v>592.0</v>
+        <v>668.0</v>
       </c>
       <c r="K135" t="n">
         <v>1.0</v>
@@ -9692,13 +9692,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" t="n">
-        <v>591.0</v>
+        <v>667.0</v>
       </c>
       <c r="O135" t="n">
-        <v>282.0</v>
+        <v>327.0</v>
       </c>
       <c r="P135" t="n">
-        <v>228.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q135" t="n">
         <v>82.0</v>
@@ -9751,7 +9751,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" t="n">
-        <v>485.0</v>
+        <v>534.0</v>
       </c>
       <c r="K136" t="n">
         <v>1.0</v>
@@ -9763,16 +9763,16 @@
         <v>0.0</v>
       </c>
       <c r="N136" t="n">
-        <v>485.0</v>
+        <v>534.0</v>
       </c>
       <c r="O136" t="n">
-        <v>262.0</v>
+        <v>284.0</v>
       </c>
       <c r="P136" t="n">
-        <v>219.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q136" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="R136" t="n">
         <v>16.0</v>
@@ -9822,7 +9822,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" t="n">
-        <v>296.0</v>
+        <v>338.0</v>
       </c>
       <c r="K137" t="n">
         <v>1.0</v>
@@ -9834,19 +9834,19 @@
         <v>0.0</v>
       </c>
       <c r="N137" t="n">
-        <v>296.0</v>
+        <v>338.0</v>
       </c>
       <c r="O137" t="n">
-        <v>89.0</v>
+        <v>110.0</v>
       </c>
       <c r="P137" t="n">
-        <v>194.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q137" t="n">
         <v>13.0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="S137" t="n">
         <v>0.0</v>
@@ -9861,7 +9861,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="138">
@@ -9893,7 +9893,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" t="n">
-        <v>517.0</v>
+        <v>598.0</v>
       </c>
       <c r="K138" t="n">
         <v>1.0</v>
@@ -9905,13 +9905,13 @@
         <v>0.0</v>
       </c>
       <c r="N138" t="n">
-        <v>517.0</v>
+        <v>598.0</v>
       </c>
       <c r="O138" t="n">
-        <v>255.0</v>
+        <v>307.0</v>
       </c>
       <c r="P138" t="n">
-        <v>238.0</v>
+        <v>267.0</v>
       </c>
       <c r="Q138" t="n">
         <v>24.0</v>
@@ -9926,13 +9926,13 @@
         <v>0.0</v>
       </c>
       <c r="U138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V138" t="n">
         <v>0.0</v>
       </c>
       <c r="W138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -9988,10 +9988,10 @@
         <v>21.0</v>
       </c>
       <c r="R139" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="S139" t="n">
-        <v>12.0</v>
+        <v>21.0</v>
       </c>
       <c r="T139" t="n">
         <v>0.0</v>
@@ -10003,7 +10003,7 @@
         <v>0.0</v>
       </c>
       <c r="W139" t="n">
-        <v>18.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="140">
@@ -10035,7 +10035,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" t="n">
-        <v>556.0</v>
+        <v>597.0</v>
       </c>
       <c r="K140" t="n">
         <v>1.0</v>
@@ -10047,13 +10047,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" t="n">
-        <v>556.0</v>
+        <v>597.0</v>
       </c>
       <c r="O140" t="n">
-        <v>273.0</v>
+        <v>292.0</v>
       </c>
       <c r="P140" t="n">
-        <v>282.0</v>
+        <v>304.0</v>
       </c>
       <c r="Q140" t="n">
         <v>1.0</v>
@@ -10068,13 +10068,13 @@
         <v>0.0</v>
       </c>
       <c r="U140" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="V140" t="n">
         <v>0.0</v>
       </c>
       <c r="W140" t="n">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="141">
@@ -10106,7 +10106,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" t="n">
-        <v>458.0</v>
+        <v>506.0</v>
       </c>
       <c r="K141" t="n">
         <v>1.0</v>
@@ -10118,13 +10118,13 @@
         <v>1.0</v>
       </c>
       <c r="N141" t="n">
-        <v>457.0</v>
+        <v>505.0</v>
       </c>
       <c r="O141" t="n">
-        <v>245.0</v>
+        <v>277.0</v>
       </c>
       <c r="P141" t="n">
-        <v>213.0</v>
+        <v>229.0</v>
       </c>
       <c r="Q141" t="n">
         <v>0.0</v>
@@ -10177,7 +10177,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" t="n">
-        <v>706.0</v>
+        <v>764.0</v>
       </c>
       <c r="K142" t="n">
         <v>1.0</v>
@@ -10189,19 +10189,19 @@
         <v>0.0</v>
       </c>
       <c r="N142" t="n">
-        <v>706.0</v>
+        <v>764.0</v>
       </c>
       <c r="O142" t="n">
-        <v>383.0</v>
+        <v>408.0</v>
       </c>
       <c r="P142" t="n">
-        <v>323.0</v>
+        <v>356.0</v>
       </c>
       <c r="Q142" t="n">
         <v>0.0</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S142" t="n">
         <v>0.0</v>
@@ -10216,7 +10216,7 @@
         <v>0.0</v>
       </c>
       <c r="W142" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="143">
@@ -10248,7 +10248,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" t="n">
-        <v>369.0</v>
+        <v>439.0</v>
       </c>
       <c r="K143" t="n">
         <v>1.0</v>
@@ -10257,16 +10257,16 @@
         <v>1.0</v>
       </c>
       <c r="M143" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N143" t="n">
-        <v>369.0</v>
+        <v>438.0</v>
       </c>
       <c r="O143" t="n">
-        <v>204.0</v>
+        <v>256.0</v>
       </c>
       <c r="P143" t="n">
-        <v>165.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q143" t="n">
         <v>0.0</v>
@@ -10319,7 +10319,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" t="n">
-        <v>590.0</v>
+        <v>694.0</v>
       </c>
       <c r="K144" t="n">
         <v>1.0</v>
@@ -10331,13 +10331,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" t="n">
-        <v>590.0</v>
+        <v>694.0</v>
       </c>
       <c r="O144" t="n">
-        <v>308.0</v>
+        <v>355.0</v>
       </c>
       <c r="P144" t="n">
-        <v>282.0</v>
+        <v>339.0</v>
       </c>
       <c r="Q144" t="n">
         <v>0.0</v>
@@ -10390,7 +10390,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" t="n">
-        <v>453.0</v>
+        <v>474.0</v>
       </c>
       <c r="K145" t="n">
         <v>1.0</v>
@@ -10402,22 +10402,22 @@
         <v>0.0</v>
       </c>
       <c r="N145" t="n">
-        <v>453.0</v>
+        <v>474.0</v>
       </c>
       <c r="O145" t="n">
-        <v>189.0</v>
+        <v>195.0</v>
       </c>
       <c r="P145" t="n">
-        <v>250.0</v>
+        <v>264.0</v>
       </c>
       <c r="Q145" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R145" t="n">
         <v>10.0</v>
       </c>
       <c r="S145" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="T145" t="n">
         <v>0.0</v>
@@ -10429,7 +10429,7 @@
         <v>1.0</v>
       </c>
       <c r="W145" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="146">
@@ -10461,7 +10461,7 @@
         <v>863.0</v>
       </c>
       <c r="J146" t="n">
-        <v>211.0</v>
+        <v>259.0</v>
       </c>
       <c r="K146" t="n">
         <v>1.0</v>
@@ -10473,19 +10473,19 @@
         <v>2.0</v>
       </c>
       <c r="N146" t="n">
-        <v>209.0</v>
+        <v>257.0</v>
       </c>
       <c r="O146" t="n">
-        <v>82.0</v>
+        <v>108.0</v>
       </c>
       <c r="P146" t="n">
-        <v>129.0</v>
+        <v>151.0</v>
       </c>
       <c r="Q146" t="n">
         <v>0.0</v>
       </c>
       <c r="R146" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="S146" t="n">
         <v>1.0</v>
@@ -10500,7 +10500,7 @@
         <v>0.0</v>
       </c>
       <c r="W146" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="147">
@@ -10603,7 +10603,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" t="n">
-        <v>479.0</v>
+        <v>493.0</v>
       </c>
       <c r="K148" t="n">
         <v>1.0</v>
@@ -10615,13 +10615,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" t="n">
-        <v>479.0</v>
+        <v>493.0</v>
       </c>
       <c r="O148" t="n">
-        <v>124.0</v>
+        <v>135.0</v>
       </c>
       <c r="P148" t="n">
-        <v>355.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q148" t="n">
         <v>0.0</v>
@@ -10674,7 +10674,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" t="n">
-        <v>212.0</v>
+        <v>322.0</v>
       </c>
       <c r="K149" t="n">
         <v>1.0</v>
@@ -10686,16 +10686,16 @@
         <v>0.0</v>
       </c>
       <c r="N149" t="n">
-        <v>212.0</v>
+        <v>322.0</v>
       </c>
       <c r="O149" t="n">
-        <v>121.0</v>
+        <v>176.0</v>
       </c>
       <c r="P149" t="n">
-        <v>91.0</v>
+        <v>144.0</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R149" t="n">
         <v>0.0</v>
@@ -10816,7 +10816,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="K151" t="n">
         <v>1.0</v>
@@ -10828,10 +10828,10 @@
         <v>0.0</v>
       </c>
       <c r="N151" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="O151" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="P151" t="n">
         <v>160.0</v>
@@ -10887,7 +10887,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" t="n">
-        <v>405.0</v>
+        <v>443.0</v>
       </c>
       <c r="K152" t="n">
         <v>1.0</v>
@@ -10899,13 +10899,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" t="n">
-        <v>404.0</v>
+        <v>442.0</v>
       </c>
       <c r="O152" t="n">
-        <v>192.0</v>
+        <v>212.0</v>
       </c>
       <c r="P152" t="n">
-        <v>213.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q152" t="n">
         <v>0.0</v>
@@ -10958,7 +10958,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" t="n">
-        <v>564.0</v>
+        <v>587.0</v>
       </c>
       <c r="K153" t="n">
         <v>1.0</v>
@@ -10970,13 +10970,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" t="n">
-        <v>564.0</v>
+        <v>587.0</v>
       </c>
       <c r="O153" t="n">
-        <v>276.0</v>
+        <v>288.0</v>
       </c>
       <c r="P153" t="n">
-        <v>288.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q153" t="n">
         <v>0.0</v>
@@ -11029,7 +11029,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" t="n">
-        <v>509.0</v>
+        <v>513.0</v>
       </c>
       <c r="K154" t="n">
         <v>1.0</v>
@@ -11041,7 +11041,7 @@
         <v>0.0</v>
       </c>
       <c r="N154" t="n">
-        <v>509.0</v>
+        <v>513.0</v>
       </c>
       <c r="O154" t="n">
         <v>29.0</v>
@@ -11050,7 +11050,7 @@
         <v>291.0</v>
       </c>
       <c r="Q154" t="n">
-        <v>189.0</v>
+        <v>193.0</v>
       </c>
       <c r="R154" t="n">
         <v>0.0</v>
@@ -11100,7 +11100,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" t="n">
-        <v>691.0</v>
+        <v>701.0</v>
       </c>
       <c r="K155" t="n">
         <v>1.0</v>
@@ -11112,13 +11112,13 @@
         <v>0.0</v>
       </c>
       <c r="N155" t="n">
-        <v>691.0</v>
+        <v>701.0</v>
       </c>
       <c r="O155" t="n">
-        <v>337.0</v>
+        <v>345.0</v>
       </c>
       <c r="P155" t="n">
-        <v>354.0</v>
+        <v>356.0</v>
       </c>
       <c r="Q155" t="n">
         <v>0.0</v>
@@ -11171,7 +11171,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" t="n">
-        <v>496.0</v>
+        <v>528.0</v>
       </c>
       <c r="K156" t="n">
         <v>1.0</v>
@@ -11183,13 +11183,13 @@
         <v>0.0</v>
       </c>
       <c r="N156" t="n">
-        <v>496.0</v>
+        <v>528.0</v>
       </c>
       <c r="O156" t="n">
-        <v>165.0</v>
+        <v>172.0</v>
       </c>
       <c r="P156" t="n">
-        <v>330.0</v>
+        <v>355.0</v>
       </c>
       <c r="Q156" t="n">
         <v>1.0</v>
@@ -11242,7 +11242,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" t="n">
-        <v>444.0</v>
+        <v>487.0</v>
       </c>
       <c r="K157" t="n">
         <v>1.0</v>
@@ -11254,13 +11254,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" t="n">
-        <v>440.0</v>
+        <v>483.0</v>
       </c>
       <c r="O157" t="n">
-        <v>118.0</v>
+        <v>141.0</v>
       </c>
       <c r="P157" t="n">
-        <v>326.0</v>
+        <v>346.0</v>
       </c>
       <c r="Q157" t="n">
         <v>0.0</v>
@@ -11313,7 +11313,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" t="n">
-        <v>535.0</v>
+        <v>605.0</v>
       </c>
       <c r="K158" t="n">
         <v>1.0</v>
@@ -11325,13 +11325,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" t="n">
-        <v>535.0</v>
+        <v>605.0</v>
       </c>
       <c r="O158" t="n">
-        <v>240.0</v>
+        <v>275.0</v>
       </c>
       <c r="P158" t="n">
-        <v>295.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q158" t="n">
         <v>0.0</v>
@@ -11384,7 +11384,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" t="n">
-        <v>596.0</v>
+        <v>615.0</v>
       </c>
       <c r="K159" t="n">
         <v>1.0</v>
@@ -11396,13 +11396,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" t="n">
-        <v>595.0</v>
+        <v>614.0</v>
       </c>
       <c r="O159" t="n">
-        <v>334.0</v>
+        <v>346.0</v>
       </c>
       <c r="P159" t="n">
-        <v>262.0</v>
+        <v>269.0</v>
       </c>
       <c r="Q159" t="n">
         <v>0.0</v>
@@ -11411,7 +11411,7 @@
         <v>21.0</v>
       </c>
       <c r="S159" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T159" t="n">
         <v>0.0</v>
@@ -11423,7 +11423,7 @@
         <v>0.0</v>
       </c>
       <c r="W159" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="160">
@@ -11455,7 +11455,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" t="n">
-        <v>778.0</v>
+        <v>787.0</v>
       </c>
       <c r="K160" t="n">
         <v>1.0</v>
@@ -11467,13 +11467,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" t="n">
-        <v>778.0</v>
+        <v>787.0</v>
       </c>
       <c r="O160" t="n">
-        <v>385.0</v>
+        <v>390.0</v>
       </c>
       <c r="P160" t="n">
-        <v>393.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q160" t="n">
         <v>0.0</v>
@@ -11597,7 +11597,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" t="n">
-        <v>600.0</v>
+        <v>625.0</v>
       </c>
       <c r="K162" t="n">
         <v>1.0</v>
@@ -11609,16 +11609,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" t="n">
-        <v>599.0</v>
+        <v>624.0</v>
       </c>
       <c r="O162" t="n">
         <v>13.0</v>
       </c>
       <c r="P162" t="n">
-        <v>140.0</v>
+        <v>149.0</v>
       </c>
       <c r="Q162" t="n">
-        <v>447.0</v>
+        <v>463.0</v>
       </c>
       <c r="R162" t="n">
         <v>0.0</v>
@@ -11668,7 +11668,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" t="n">
-        <v>615.0</v>
+        <v>656.0</v>
       </c>
       <c r="K163" t="n">
         <v>1.0</v>
@@ -11680,16 +11680,16 @@
         <v>0.0</v>
       </c>
       <c r="N163" t="n">
-        <v>615.0</v>
+        <v>656.0</v>
       </c>
       <c r="O163" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="P163" t="n">
-        <v>277.0</v>
+        <v>298.0</v>
       </c>
       <c r="Q163" t="n">
-        <v>333.0</v>
+        <v>350.0</v>
       </c>
       <c r="R163" t="n">
         <v>0.0</v>
@@ -11739,7 +11739,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" t="n">
-        <v>615.0</v>
+        <v>633.0</v>
       </c>
       <c r="K164" t="n">
         <v>1.0</v>
@@ -11751,16 +11751,16 @@
         <v>1.0</v>
       </c>
       <c r="N164" t="n">
-        <v>614.0</v>
+        <v>632.0</v>
       </c>
       <c r="O164" t="n">
         <v>1.0</v>
       </c>
       <c r="P164" t="n">
-        <v>262.0</v>
+        <v>272.0</v>
       </c>
       <c r="Q164" t="n">
-        <v>352.0</v>
+        <v>360.0</v>
       </c>
       <c r="R164" t="n">
         <v>0.0</v>
@@ -11810,7 +11810,7 @@
         <v>421.0</v>
       </c>
       <c r="J165" t="n">
-        <v>307.0</v>
+        <v>331.0</v>
       </c>
       <c r="K165" t="n">
         <v>1.0</v>
@@ -11822,34 +11822,34 @@
         <v>0.0</v>
       </c>
       <c r="N165" t="n">
-        <v>307.0</v>
+        <v>331.0</v>
       </c>
       <c r="O165" t="n">
-        <v>166.0</v>
+        <v>181.0</v>
       </c>
       <c r="P165" t="n">
-        <v>136.0</v>
+        <v>143.0</v>
       </c>
       <c r="Q165" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S165" t="n">
         <v>5.0</v>
       </c>
-      <c r="R165" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S165" t="n">
-        <v>3.0</v>
-      </c>
       <c r="T165" t="n">
         <v>0.0</v>
       </c>
       <c r="U165" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="V165" t="n">
         <v>0.0</v>
       </c>
       <c r="W165" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="166">
@@ -11881,7 +11881,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" t="n">
-        <v>466.0</v>
+        <v>501.0</v>
       </c>
       <c r="K166" t="n">
         <v>1.0</v>
@@ -11893,13 +11893,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" t="n">
-        <v>466.0</v>
+        <v>501.0</v>
       </c>
       <c r="O166" t="n">
-        <v>243.0</v>
+        <v>261.0</v>
       </c>
       <c r="P166" t="n">
-        <v>223.0</v>
+        <v>240.0</v>
       </c>
       <c r="Q166" t="n">
         <v>0.0</v>
@@ -11952,7 +11952,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" t="n">
-        <v>469.0</v>
+        <v>504.0</v>
       </c>
       <c r="K167" t="n">
         <v>1.0</v>
@@ -11964,19 +11964,19 @@
         <v>0.0</v>
       </c>
       <c r="N167" t="n">
-        <v>469.0</v>
+        <v>504.0</v>
       </c>
       <c r="O167" t="n">
-        <v>221.0</v>
+        <v>242.0</v>
       </c>
       <c r="P167" t="n">
-        <v>248.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q167" t="n">
         <v>0.0</v>
       </c>
       <c r="R167" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S167" t="n">
         <v>0.0</v>
@@ -11991,7 +11991,7 @@
         <v>0.0</v>
       </c>
       <c r="W167" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="168">
@@ -12023,7 +12023,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" t="n">
-        <v>395.0</v>
+        <v>445.0</v>
       </c>
       <c r="K168" t="n">
         <v>1.0</v>
@@ -12035,13 +12035,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" t="n">
-        <v>395.0</v>
+        <v>445.0</v>
       </c>
       <c r="O168" t="n">
-        <v>100.0</v>
+        <v>123.0</v>
       </c>
       <c r="P168" t="n">
-        <v>207.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q168" t="n">
         <v>88.0</v>
@@ -12094,7 +12094,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" t="n">
-        <v>318.0</v>
+        <v>319.0</v>
       </c>
       <c r="K169" t="n">
         <v>1.0</v>
@@ -12106,10 +12106,10 @@
         <v>0.0</v>
       </c>
       <c r="N169" t="n">
-        <v>318.0</v>
+        <v>319.0</v>
       </c>
       <c r="O169" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="P169" t="n">
         <v>197.0</v>
@@ -12165,7 +12165,7 @@
         <v>968.0</v>
       </c>
       <c r="J170" t="n">
-        <v>569.0</v>
+        <v>684.0</v>
       </c>
       <c r="K170" t="n">
         <v>1.0</v>
@@ -12177,16 +12177,16 @@
         <v>0.0</v>
       </c>
       <c r="N170" t="n">
-        <v>569.0</v>
+        <v>684.0</v>
       </c>
       <c r="O170" t="n">
         <v>54.0</v>
       </c>
       <c r="P170" t="n">
-        <v>261.0</v>
+        <v>317.0</v>
       </c>
       <c r="Q170" t="n">
-        <v>254.0</v>
+        <v>313.0</v>
       </c>
       <c r="R170" t="n">
         <v>0.0</v>
@@ -12307,7 +12307,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" t="n">
-        <v>183.0</v>
+        <v>247.0</v>
       </c>
       <c r="K172" t="n">
         <v>1.0</v>
@@ -12319,13 +12319,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" t="n">
-        <v>183.0</v>
+        <v>247.0</v>
       </c>
       <c r="O172" t="n">
-        <v>22.0</v>
+        <v>70.0</v>
       </c>
       <c r="P172" t="n">
-        <v>161.0</v>
+        <v>177.0</v>
       </c>
       <c r="Q172" t="n">
         <v>0.0</v>
@@ -12378,7 +12378,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" t="n">
-        <v>800.0</v>
+        <v>839.0</v>
       </c>
       <c r="K173" t="n">
         <v>1.0</v>
@@ -12390,13 +12390,13 @@
         <v>0.0</v>
       </c>
       <c r="N173" t="n">
-        <v>800.0</v>
+        <v>839.0</v>
       </c>
       <c r="O173" t="n">
-        <v>393.0</v>
+        <v>429.0</v>
       </c>
       <c r="P173" t="n">
-        <v>407.0</v>
+        <v>410.0</v>
       </c>
       <c r="Q173" t="n">
         <v>0.0</v>
@@ -12449,7 +12449,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" t="n">
-        <v>751.0</v>
+        <v>829.0</v>
       </c>
       <c r="K174" t="n">
         <v>1.0</v>
@@ -12461,13 +12461,13 @@
         <v>0.0</v>
       </c>
       <c r="N174" t="n">
-        <v>751.0</v>
+        <v>829.0</v>
       </c>
       <c r="O174" t="n">
-        <v>365.0</v>
+        <v>410.0</v>
       </c>
       <c r="P174" t="n">
-        <v>386.0</v>
+        <v>419.0</v>
       </c>
       <c r="Q174" t="n">
         <v>0.0</v>
@@ -12520,7 +12520,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" t="n">
-        <v>695.0</v>
+        <v>739.0</v>
       </c>
       <c r="K175" t="n">
         <v>1.0</v>
@@ -12532,13 +12532,13 @@
         <v>0.0</v>
       </c>
       <c r="N175" t="n">
-        <v>695.0</v>
+        <v>739.0</v>
       </c>
       <c r="O175" t="n">
-        <v>323.0</v>
+        <v>346.0</v>
       </c>
       <c r="P175" t="n">
-        <v>372.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q175" t="n">
         <v>0.0</v>
@@ -12591,7 +12591,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" t="n">
-        <v>337.0</v>
+        <v>357.0</v>
       </c>
       <c r="K176" t="n">
         <v>1.0</v>
@@ -12603,19 +12603,19 @@
         <v>0.0</v>
       </c>
       <c r="N176" t="n">
-        <v>337.0</v>
+        <v>357.0</v>
       </c>
       <c r="O176" t="n">
-        <v>137.0</v>
+        <v>143.0</v>
       </c>
       <c r="P176" t="n">
-        <v>200.0</v>
+        <v>214.0</v>
       </c>
       <c r="Q176" t="n">
         <v>0.0</v>
       </c>
       <c r="R176" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="S176" t="n">
         <v>0.0</v>
@@ -12630,7 +12630,7 @@
         <v>0.0</v>
       </c>
       <c r="W176" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="177">
@@ -12662,7 +12662,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" t="n">
-        <v>265.0</v>
+        <v>298.0</v>
       </c>
       <c r="K177" t="n">
         <v>1.0</v>
@@ -12674,19 +12674,19 @@
         <v>0.0</v>
       </c>
       <c r="N177" t="n">
-        <v>265.0</v>
+        <v>298.0</v>
       </c>
       <c r="O177" t="n">
-        <v>115.0</v>
+        <v>127.0</v>
       </c>
       <c r="P177" t="n">
-        <v>150.0</v>
+        <v>171.0</v>
       </c>
       <c r="Q177" t="n">
         <v>0.0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S177" t="n">
         <v>0.0</v>
@@ -12701,7 +12701,7 @@
         <v>0.0</v>
       </c>
       <c r="W177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="178">
@@ -12733,7 +12733,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
       <c r="K178" t="n">
         <v>1.0</v>
@@ -12745,10 +12745,10 @@
         <v>0.0</v>
       </c>
       <c r="N178" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
       <c r="O178" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="P178" t="n">
         <v>160.0</v>
@@ -12757,7 +12757,7 @@
         <v>1.0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="S178" t="n">
         <v>0.0</v>
@@ -12766,13 +12766,13 @@
         <v>0.0</v>
       </c>
       <c r="U178" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="V178" t="n">
         <v>0.0</v>
       </c>
       <c r="W178" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="179">
@@ -12804,7 +12804,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" t="n">
-        <v>425.0</v>
+        <v>466.0</v>
       </c>
       <c r="K179" t="n">
         <v>1.0</v>
@@ -12816,19 +12816,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" t="n">
-        <v>425.0</v>
+        <v>466.0</v>
       </c>
       <c r="O179" t="n">
-        <v>250.0</v>
+        <v>273.0</v>
       </c>
       <c r="P179" t="n">
-        <v>175.0</v>
+        <v>193.0</v>
       </c>
       <c r="Q179" t="n">
         <v>0.0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="S179" t="n">
         <v>0.0</v>
@@ -12843,7 +12843,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="180">
@@ -12875,7 +12875,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" t="n">
-        <v>290.0</v>
+        <v>315.0</v>
       </c>
       <c r="K180" t="n">
         <v>1.0</v>
@@ -12887,13 +12887,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" t="n">
-        <v>290.0</v>
+        <v>315.0</v>
       </c>
       <c r="O180" t="n">
-        <v>150.0</v>
+        <v>163.0</v>
       </c>
       <c r="P180" t="n">
-        <v>140.0</v>
+        <v>152.0</v>
       </c>
       <c r="Q180" t="n">
         <v>0.0</v>
@@ -12970,7 +12970,7 @@
         <v>0.0</v>
       </c>
       <c r="R181" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S181" t="n">
         <v>0.0</v>
@@ -12979,13 +12979,13 @@
         <v>0.0</v>
       </c>
       <c r="U181" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V181" t="n">
         <v>0.0</v>
       </c>
       <c r="W181" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="182">
@@ -13017,7 +13017,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" t="n">
-        <v>486.0</v>
+        <v>502.0</v>
       </c>
       <c r="K182" t="n">
         <v>1.0</v>
@@ -13029,13 +13029,13 @@
         <v>0.0</v>
       </c>
       <c r="N182" t="n">
-        <v>486.0</v>
+        <v>502.0</v>
       </c>
       <c r="O182" t="n">
-        <v>215.0</v>
+        <v>224.0</v>
       </c>
       <c r="P182" t="n">
-        <v>270.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q182" t="n">
         <v>1.0</v>
@@ -13088,7 +13088,7 @@
         <v>996.0</v>
       </c>
       <c r="J183" t="n">
-        <v>832.0</v>
+        <v>882.0</v>
       </c>
       <c r="K183" t="n">
         <v>1.0</v>
@@ -13100,13 +13100,13 @@
         <v>0.0</v>
       </c>
       <c r="N183" t="n">
-        <v>832.0</v>
+        <v>882.0</v>
       </c>
       <c r="O183" t="n">
-        <v>387.0</v>
+        <v>411.0</v>
       </c>
       <c r="P183" t="n">
-        <v>445.0</v>
+        <v>471.0</v>
       </c>
       <c r="Q183" t="n">
         <v>0.0</v>
@@ -13115,7 +13115,7 @@
         <v>26.0</v>
       </c>
       <c r="S183" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="T183" t="n">
         <v>0.0</v>
@@ -13127,7 +13127,7 @@
         <v>1.0</v>
       </c>
       <c r="W183" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="184">
@@ -13159,7 +13159,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" t="n">
-        <v>220.0</v>
+        <v>236.0</v>
       </c>
       <c r="K184" t="n">
         <v>1.0</v>
@@ -13171,13 +13171,13 @@
         <v>1.0</v>
       </c>
       <c r="N184" t="n">
-        <v>219.0</v>
+        <v>235.0</v>
       </c>
       <c r="O184" t="n">
-        <v>101.0</v>
+        <v>113.0</v>
       </c>
       <c r="P184" t="n">
-        <v>118.0</v>
+        <v>122.0</v>
       </c>
       <c r="Q184" t="n">
         <v>1.0</v>
@@ -13301,7 +13301,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" t="n">
-        <v>460.0</v>
+        <v>529.0</v>
       </c>
       <c r="K186" t="n">
         <v>1.0</v>
@@ -13313,16 +13313,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" t="n">
-        <v>460.0</v>
+        <v>529.0</v>
       </c>
       <c r="O186" t="n">
         <v>118.0</v>
       </c>
       <c r="P186" t="n">
-        <v>233.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q186" t="n">
-        <v>109.0</v>
+        <v>152.0</v>
       </c>
       <c r="R186" t="n">
         <v>1.0</v>
@@ -13372,7 +13372,7 @@
         <v>990.0</v>
       </c>
       <c r="J187" t="n">
-        <v>622.0</v>
+        <v>643.0</v>
       </c>
       <c r="K187" t="n">
         <v>1.0</v>
@@ -13384,13 +13384,13 @@
         <v>0.0</v>
       </c>
       <c r="N187" t="n">
-        <v>622.0</v>
+        <v>643.0</v>
       </c>
       <c r="O187" t="n">
-        <v>376.0</v>
+        <v>390.0</v>
       </c>
       <c r="P187" t="n">
-        <v>246.0</v>
+        <v>253.0</v>
       </c>
       <c r="Q187" t="n">
         <v>0.0</v>
@@ -13443,7 +13443,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="K188" t="n">
         <v>1.0</v>
@@ -13455,10 +13455,10 @@
         <v>0.0</v>
       </c>
       <c r="N188" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
       <c r="O188" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="P188" t="n">
         <v>325.0</v>
@@ -13467,10 +13467,10 @@
         <v>58.0</v>
       </c>
       <c r="R188" t="n">
-        <v>0.0</v>
+        <v>59.0</v>
       </c>
       <c r="S188" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="T188" t="n">
         <v>0.0</v>
@@ -13482,7 +13482,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" t="n">
-        <v>0.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="189">
@@ -13514,7 +13514,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" t="n">
-        <v>386.0</v>
+        <v>476.0</v>
       </c>
       <c r="K189" t="n">
         <v>1.0</v>
@@ -13526,13 +13526,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" t="n">
-        <v>386.0</v>
+        <v>476.0</v>
       </c>
       <c r="O189" t="n">
-        <v>23.0</v>
+        <v>90.0</v>
       </c>
       <c r="P189" t="n">
-        <v>93.0</v>
+        <v>116.0</v>
       </c>
       <c r="Q189" t="n">
         <v>270.0</v>
@@ -13585,7 +13585,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" t="n">
-        <v>575.0</v>
+        <v>627.0</v>
       </c>
       <c r="K190" t="n">
         <v>1.0</v>
@@ -13597,22 +13597,22 @@
         <v>0.0</v>
       </c>
       <c r="N190" t="n">
-        <v>575.0</v>
+        <v>627.0</v>
       </c>
       <c r="O190" t="n">
-        <v>265.0</v>
+        <v>308.0</v>
       </c>
       <c r="P190" t="n">
-        <v>289.0</v>
+        <v>298.0</v>
       </c>
       <c r="Q190" t="n">
         <v>21.0</v>
       </c>
       <c r="R190" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="S190" t="n">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="T190" t="n">
         <v>0.0</v>
@@ -13624,7 +13624,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" t="n">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="191">
@@ -13656,7 +13656,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" t="n">
-        <v>350.0</v>
+        <v>450.0</v>
       </c>
       <c r="K191" t="n">
         <v>1.0</v>
@@ -13668,13 +13668,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" t="n">
-        <v>350.0</v>
+        <v>450.0</v>
       </c>
       <c r="O191" t="n">
-        <v>105.0</v>
+        <v>162.0</v>
       </c>
       <c r="P191" t="n">
-        <v>212.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q191" t="n">
         <v>33.0</v>
@@ -13869,7 +13869,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" t="n">
-        <v>214.0</v>
+        <v>237.0</v>
       </c>
       <c r="K194" t="n">
         <v>1.0</v>
@@ -13881,16 +13881,16 @@
         <v>0.0</v>
       </c>
       <c r="N194" t="n">
-        <v>214.0</v>
+        <v>237.0</v>
       </c>
       <c r="O194" t="n">
         <v>79.0</v>
       </c>
       <c r="P194" t="n">
-        <v>135.0</v>
+        <v>149.0</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="R194" t="n">
         <v>0.0</v>
@@ -13940,7 +13940,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" t="n">
-        <v>257.0</v>
+        <v>273.0</v>
       </c>
       <c r="K195" t="n">
         <v>1.0</v>
@@ -13952,16 +13952,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" t="n">
-        <v>257.0</v>
+        <v>273.0</v>
       </c>
       <c r="O195" t="n">
         <v>71.0</v>
       </c>
       <c r="P195" t="n">
-        <v>115.0</v>
+        <v>124.0</v>
       </c>
       <c r="Q195" t="n">
-        <v>71.0</v>
+        <v>78.0</v>
       </c>
       <c r="R195" t="n">
         <v>0.0</v>
@@ -14011,7 +14011,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" t="n">
-        <v>950.0</v>
+        <v>966.0</v>
       </c>
       <c r="K196" t="n">
         <v>1.0</v>
@@ -14023,16 +14023,16 @@
         <v>0.0</v>
       </c>
       <c r="N196" t="n">
-        <v>950.0</v>
+        <v>966.0</v>
       </c>
       <c r="O196" t="n">
         <v>369.0</v>
       </c>
       <c r="P196" t="n">
-        <v>412.0</v>
+        <v>415.0</v>
       </c>
       <c r="Q196" t="n">
-        <v>169.0</v>
+        <v>182.0</v>
       </c>
       <c r="R196" t="n">
         <v>0.0</v>
@@ -14082,7 +14082,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" t="n">
-        <v>909.0</v>
+        <v>991.0</v>
       </c>
       <c r="K197" t="n">
         <v>1.0</v>
@@ -14094,16 +14094,16 @@
         <v>0.0</v>
       </c>
       <c r="N197" t="n">
-        <v>909.0</v>
+        <v>991.0</v>
       </c>
       <c r="O197" t="n">
-        <v>543.0</v>
+        <v>548.0</v>
       </c>
       <c r="P197" t="n">
-        <v>316.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q197" t="n">
-        <v>50.0</v>
+        <v>113.0</v>
       </c>
       <c r="R197" t="n">
         <v>0.0</v>
@@ -14153,7 +14153,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" t="n">
-        <v>1071.0</v>
+        <v>1081.0</v>
       </c>
       <c r="K198" t="n">
         <v>1.0</v>
@@ -14165,13 +14165,13 @@
         <v>0.0</v>
       </c>
       <c r="N198" t="n">
-        <v>1071.0</v>
+        <v>1081.0</v>
       </c>
       <c r="O198" t="n">
-        <v>307.0</v>
+        <v>312.0</v>
       </c>
       <c r="P198" t="n">
-        <v>523.0</v>
+        <v>528.0</v>
       </c>
       <c r="Q198" t="n">
         <v>241.0</v>
@@ -14180,7 +14180,7 @@
         <v>0.0</v>
       </c>
       <c r="S198" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T198" t="n">
         <v>0.0</v>
@@ -14192,7 +14192,7 @@
         <v>0.0</v>
       </c>
       <c r="W198" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="199">
@@ -14295,7 +14295,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" t="n">
-        <v>390.0</v>
+        <v>396.0</v>
       </c>
       <c r="K200" t="n">
         <v>1.0</v>
@@ -14307,25 +14307,25 @@
         <v>0.0</v>
       </c>
       <c r="N200" t="n">
-        <v>390.0</v>
+        <v>396.0</v>
       </c>
       <c r="O200" t="n">
-        <v>230.0</v>
+        <v>233.0</v>
       </c>
       <c r="P200" t="n">
-        <v>157.0</v>
+        <v>160.0</v>
       </c>
       <c r="Q200" t="n">
         <v>3.0</v>
       </c>
       <c r="R200" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S200" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T200" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U200" t="n">
         <v>0.0</v>
@@ -14334,7 +14334,7 @@
         <v>0.0</v>
       </c>
       <c r="W200" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="201">
@@ -14366,7 +14366,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" t="n">
-        <v>610.0</v>
+        <v>636.0</v>
       </c>
       <c r="K201" t="n">
         <v>1.0</v>
@@ -14378,19 +14378,19 @@
         <v>0.0</v>
       </c>
       <c r="N201" t="n">
-        <v>610.0</v>
+        <v>636.0</v>
       </c>
       <c r="O201" t="n">
-        <v>312.0</v>
+        <v>329.0</v>
       </c>
       <c r="P201" t="n">
-        <v>295.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R201" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S201" t="n">
         <v>16.0</v>
@@ -14405,7 +14405,7 @@
         <v>1.0</v>
       </c>
       <c r="W201" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="202">
@@ -14437,7 +14437,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" t="n">
-        <v>245.0</v>
+        <v>284.0</v>
       </c>
       <c r="K202" t="n">
         <v>1.0</v>
@@ -14449,13 +14449,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" t="n">
-        <v>245.0</v>
+        <v>284.0</v>
       </c>
       <c r="O202" t="n">
-        <v>135.0</v>
+        <v>153.0</v>
       </c>
       <c r="P202" t="n">
-        <v>110.0</v>
+        <v>131.0</v>
       </c>
       <c r="Q202" t="n">
         <v>0.0</v>
@@ -14508,7 +14508,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" t="n">
-        <v>391.0</v>
+        <v>474.0</v>
       </c>
       <c r="K203" t="n">
         <v>1.0</v>
@@ -14520,13 +14520,13 @@
         <v>0.0</v>
       </c>
       <c r="N203" t="n">
-        <v>391.0</v>
+        <v>474.0</v>
       </c>
       <c r="O203" t="n">
-        <v>206.0</v>
+        <v>260.0</v>
       </c>
       <c r="P203" t="n">
-        <v>185.0</v>
+        <v>214.0</v>
       </c>
       <c r="Q203" t="n">
         <v>0.0</v>
@@ -14579,7 +14579,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" t="n">
-        <v>238.0</v>
+        <v>272.0</v>
       </c>
       <c r="K204" t="n">
         <v>1.0</v>
@@ -14591,13 +14591,13 @@
         <v>2.0</v>
       </c>
       <c r="N204" t="n">
-        <v>236.0</v>
+        <v>270.0</v>
       </c>
       <c r="O204" t="n">
-        <v>130.0</v>
+        <v>150.0</v>
       </c>
       <c r="P204" t="n">
-        <v>103.0</v>
+        <v>117.0</v>
       </c>
       <c r="Q204" t="n">
         <v>5.0</v>
@@ -14721,7 +14721,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" t="n">
-        <v>555.0</v>
+        <v>567.0</v>
       </c>
       <c r="K206" t="n">
         <v>1.0</v>
@@ -14733,22 +14733,22 @@
         <v>0.0</v>
       </c>
       <c r="N206" t="n">
-        <v>555.0</v>
+        <v>567.0</v>
       </c>
       <c r="O206" t="n">
-        <v>316.0</v>
+        <v>325.0</v>
       </c>
       <c r="P206" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q206" t="n">
         <v>0.0</v>
       </c>
       <c r="R206" t="n">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="S206" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T206" t="n">
         <v>0.0</v>
@@ -14760,7 +14760,7 @@
         <v>0.0</v>
       </c>
       <c r="W206" t="n">
-        <v>1.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="207">
@@ -14792,7 +14792,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" t="n">
-        <v>337.0</v>
+        <v>367.0</v>
       </c>
       <c r="K207" t="n">
         <v>1.0</v>
@@ -14804,13 +14804,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" t="n">
-        <v>337.0</v>
+        <v>367.0</v>
       </c>
       <c r="O207" t="n">
-        <v>194.0</v>
+        <v>208.0</v>
       </c>
       <c r="P207" t="n">
-        <v>139.0</v>
+        <v>155.0</v>
       </c>
       <c r="Q207" t="n">
         <v>4.0</v>
@@ -14866,7 +14866,7 @@
         <v>432.0</v>
       </c>
       <c r="K208" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L208" t="n">
         <v>1.0</v>
@@ -14934,7 +14934,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" t="n">
-        <v>694.0</v>
+        <v>703.0</v>
       </c>
       <c r="K209" t="n">
         <v>1.0</v>
@@ -14946,13 +14946,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" t="n">
-        <v>694.0</v>
+        <v>703.0</v>
       </c>
       <c r="O209" t="n">
-        <v>348.0</v>
+        <v>352.0</v>
       </c>
       <c r="P209" t="n">
-        <v>346.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q209" t="n">
         <v>0.0</v>
@@ -15005,10 +15005,10 @@
         <v>792.0</v>
       </c>
       <c r="J210" t="n">
-        <v>480.0</v>
+        <v>546.0</v>
       </c>
       <c r="K210" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L210" t="n">
         <v>1.0</v>
@@ -15017,13 +15017,13 @@
         <v>0.0</v>
       </c>
       <c r="N210" t="n">
-        <v>480.0</v>
+        <v>546.0</v>
       </c>
       <c r="O210" t="n">
-        <v>217.0</v>
+        <v>254.0</v>
       </c>
       <c r="P210" t="n">
-        <v>263.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q210" t="n">
         <v>0.0</v>
@@ -15076,7 +15076,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" t="n">
-        <v>722.0</v>
+        <v>765.0</v>
       </c>
       <c r="K211" t="n">
         <v>1.0</v>
@@ -15088,13 +15088,13 @@
         <v>0.0</v>
       </c>
       <c r="N211" t="n">
-        <v>722.0</v>
+        <v>765.0</v>
       </c>
       <c r="O211" t="n">
-        <v>366.0</v>
+        <v>393.0</v>
       </c>
       <c r="P211" t="n">
-        <v>356.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q211" t="n">
         <v>0.0</v>
@@ -15147,7 +15147,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" t="n">
-        <v>562.0</v>
+        <v>584.0</v>
       </c>
       <c r="K212" t="n">
         <v>1.0</v>
@@ -15159,16 +15159,16 @@
         <v>1.0</v>
       </c>
       <c r="N212" t="n">
-        <v>561.0</v>
+        <v>583.0</v>
       </c>
       <c r="O212" t="n">
-        <v>128.0</v>
+        <v>134.0</v>
       </c>
       <c r="P212" t="n">
-        <v>256.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q212" t="n">
-        <v>178.0</v>
+        <v>185.0</v>
       </c>
       <c r="R212" t="n">
         <v>4.0</v>
@@ -15218,7 +15218,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" t="n">
-        <v>448.0</v>
+        <v>516.0</v>
       </c>
       <c r="K213" t="n">
         <v>1.0</v>
@@ -15230,13 +15230,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" t="n">
-        <v>448.0</v>
+        <v>516.0</v>
       </c>
       <c r="O213" t="n">
-        <v>212.0</v>
+        <v>260.0</v>
       </c>
       <c r="P213" t="n">
-        <v>236.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q213" t="n">
         <v>0.0</v>
@@ -15289,7 +15289,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" t="n">
-        <v>358.0</v>
+        <v>365.0</v>
       </c>
       <c r="K214" t="n">
         <v>1.0</v>
@@ -15301,13 +15301,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" t="n">
-        <v>358.0</v>
+        <v>365.0</v>
       </c>
       <c r="O214" t="n">
-        <v>181.0</v>
+        <v>187.0</v>
       </c>
       <c r="P214" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="Q214" t="n">
         <v>0.0</v>
@@ -15360,7 +15360,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" t="n">
-        <v>505.0</v>
+        <v>546.0</v>
       </c>
       <c r="K215" t="n">
         <v>1.0</v>
@@ -15372,25 +15372,25 @@
         <v>0.0</v>
       </c>
       <c r="N215" t="n">
-        <v>505.0</v>
+        <v>546.0</v>
       </c>
       <c r="O215" t="n">
-        <v>196.0</v>
+        <v>216.0</v>
       </c>
       <c r="P215" t="n">
-        <v>309.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q215" t="n">
         <v>0.0</v>
       </c>
       <c r="R215" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="S215" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T215" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="U215" t="n">
         <v>0.0</v>
@@ -15399,7 +15399,7 @@
         <v>0.0</v>
       </c>
       <c r="W215" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="216">
@@ -15431,7 +15431,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" t="n">
-        <v>215.0</v>
+        <v>239.0</v>
       </c>
       <c r="K216" t="n">
         <v>1.0</v>
@@ -15443,16 +15443,16 @@
         <v>0.0</v>
       </c>
       <c r="N216" t="n">
-        <v>215.0</v>
+        <v>239.0</v>
       </c>
       <c r="O216" t="n">
-        <v>123.0</v>
+        <v>132.0</v>
       </c>
       <c r="P216" t="n">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="Q216" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="R216" t="n">
         <v>0.0</v>
@@ -15502,7 +15502,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" t="n">
-        <v>474.0</v>
+        <v>545.0</v>
       </c>
       <c r="K217" t="n">
         <v>1.0</v>
@@ -15514,13 +15514,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" t="n">
-        <v>474.0</v>
+        <v>545.0</v>
       </c>
       <c r="O217" t="n">
-        <v>201.0</v>
+        <v>233.0</v>
       </c>
       <c r="P217" t="n">
-        <v>273.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q217" t="n">
         <v>0.0</v>
@@ -15573,7 +15573,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" t="n">
-        <v>413.0</v>
+        <v>451.0</v>
       </c>
       <c r="K218" t="n">
         <v>1.0</v>
@@ -15585,13 +15585,13 @@
         <v>1.0</v>
       </c>
       <c r="N218" t="n">
-        <v>412.0</v>
+        <v>450.0</v>
       </c>
       <c r="O218" t="n">
-        <v>220.0</v>
+        <v>241.0</v>
       </c>
       <c r="P218" t="n">
-        <v>193.0</v>
+        <v>210.0</v>
       </c>
       <c r="Q218" t="n">
         <v>0.0</v>
@@ -15644,7 +15644,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" t="n">
-        <v>541.0</v>
+        <v>574.0</v>
       </c>
       <c r="K219" t="n">
         <v>1.0</v>
@@ -15656,16 +15656,16 @@
         <v>0.0</v>
       </c>
       <c r="N219" t="n">
-        <v>541.0</v>
+        <v>574.0</v>
       </c>
       <c r="O219" t="n">
         <v>102.0</v>
       </c>
       <c r="P219" t="n">
-        <v>235.0</v>
+        <v>245.0</v>
       </c>
       <c r="Q219" t="n">
-        <v>204.0</v>
+        <v>227.0</v>
       </c>
       <c r="R219" t="n">
         <v>18.0</v>
@@ -15715,7 +15715,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" t="n">
-        <v>459.0</v>
+        <v>529.0</v>
       </c>
       <c r="K220" t="n">
         <v>1.0</v>
@@ -15727,16 +15727,16 @@
         <v>0.0</v>
       </c>
       <c r="N220" t="n">
-        <v>459.0</v>
+        <v>529.0</v>
       </c>
       <c r="O220" t="n">
         <v>90.0</v>
       </c>
       <c r="P220" t="n">
-        <v>212.0</v>
+        <v>247.0</v>
       </c>
       <c r="Q220" t="n">
-        <v>157.0</v>
+        <v>192.0</v>
       </c>
       <c r="R220" t="n">
         <v>0.0</v>
@@ -15786,7 +15786,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" t="n">
-        <v>486.0</v>
+        <v>503.0</v>
       </c>
       <c r="K221" t="n">
         <v>1.0</v>
@@ -15798,16 +15798,16 @@
         <v>1.0</v>
       </c>
       <c r="N221" t="n">
-        <v>485.0</v>
+        <v>502.0</v>
       </c>
       <c r="O221" t="n">
         <v>115.0</v>
       </c>
       <c r="P221" t="n">
-        <v>223.0</v>
+        <v>228.0</v>
       </c>
       <c r="Q221" t="n">
-        <v>148.0</v>
+        <v>160.0</v>
       </c>
       <c r="R221" t="n">
         <v>0.0</v>
@@ -15857,7 +15857,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" t="n">
-        <v>471.0</v>
+        <v>531.0</v>
       </c>
       <c r="K222" t="n">
         <v>1.0</v>
@@ -15869,16 +15869,16 @@
         <v>0.0</v>
       </c>
       <c r="N222" t="n">
-        <v>471.0</v>
+        <v>531.0</v>
       </c>
       <c r="O222" t="n">
         <v>126.0</v>
       </c>
       <c r="P222" t="n">
-        <v>215.0</v>
+        <v>226.0</v>
       </c>
       <c r="Q222" t="n">
-        <v>130.0</v>
+        <v>179.0</v>
       </c>
       <c r="R222" t="n">
         <v>0.0</v>
@@ -15928,7 +15928,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" t="n">
-        <v>545.0</v>
+        <v>647.0</v>
       </c>
       <c r="K223" t="n">
         <v>1.0</v>
@@ -15940,16 +15940,16 @@
         <v>0.0</v>
       </c>
       <c r="N223" t="n">
-        <v>545.0</v>
+        <v>647.0</v>
       </c>
       <c r="O223" t="n">
         <v>66.0</v>
       </c>
       <c r="P223" t="n">
-        <v>194.0</v>
+        <v>229.0</v>
       </c>
       <c r="Q223" t="n">
-        <v>285.0</v>
+        <v>352.0</v>
       </c>
       <c r="R223" t="n">
         <v>0.0</v>
@@ -16070,7 +16070,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" t="n">
-        <v>989.0</v>
+        <v>1068.0</v>
       </c>
       <c r="K225" t="n">
         <v>1.0</v>
@@ -16082,13 +16082,13 @@
         <v>0.0</v>
       </c>
       <c r="N225" t="n">
-        <v>989.0</v>
+        <v>1068.0</v>
       </c>
       <c r="O225" t="n">
-        <v>555.0</v>
+        <v>618.0</v>
       </c>
       <c r="P225" t="n">
-        <v>434.0</v>
+        <v>450.0</v>
       </c>
       <c r="Q225" t="n">
         <v>0.0</v>
@@ -16141,7 +16141,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" t="n">
-        <v>420.0</v>
+        <v>509.0</v>
       </c>
       <c r="K226" t="n">
         <v>1.0</v>
@@ -16153,19 +16153,19 @@
         <v>0.0</v>
       </c>
       <c r="N226" t="n">
-        <v>420.0</v>
+        <v>509.0</v>
       </c>
       <c r="O226" t="n">
         <v>45.0</v>
       </c>
       <c r="P226" t="n">
-        <v>206.0</v>
+        <v>250.0</v>
       </c>
       <c r="Q226" t="n">
-        <v>169.0</v>
+        <v>214.0</v>
       </c>
       <c r="R226" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="S226" t="n">
         <v>0.0</v>
@@ -16180,7 +16180,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="227">
@@ -16212,7 +16212,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" t="n">
-        <v>172.0</v>
+        <v>197.0</v>
       </c>
       <c r="K227" t="n">
         <v>1.0</v>
@@ -16224,13 +16224,13 @@
         <v>0.0</v>
       </c>
       <c r="N227" t="n">
-        <v>172.0</v>
+        <v>197.0</v>
       </c>
       <c r="O227" t="n">
-        <v>102.0</v>
+        <v>114.0</v>
       </c>
       <c r="P227" t="n">
-        <v>70.0</v>
+        <v>83.0</v>
       </c>
       <c r="Q227" t="n">
         <v>0.0</v>
@@ -16283,7 +16283,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" t="n">
-        <v>500.0</v>
+        <v>626.0</v>
       </c>
       <c r="K228" t="n">
         <v>1.0</v>
@@ -16295,16 +16295,16 @@
         <v>0.0</v>
       </c>
       <c r="N228" t="n">
-        <v>500.0</v>
+        <v>626.0</v>
       </c>
       <c r="O228" t="n">
         <v>52.0</v>
       </c>
       <c r="P228" t="n">
-        <v>202.0</v>
+        <v>264.0</v>
       </c>
       <c r="Q228" t="n">
-        <v>246.0</v>
+        <v>310.0</v>
       </c>
       <c r="R228" t="n">
         <v>0.0</v>
@@ -16354,7 +16354,7 @@
         <v>832.0</v>
       </c>
       <c r="J229" t="n">
-        <v>710.0</v>
+        <v>774.0</v>
       </c>
       <c r="K229" t="n">
         <v>1.0</v>
@@ -16366,13 +16366,13 @@
         <v>0.0</v>
       </c>
       <c r="N229" t="n">
-        <v>710.0</v>
+        <v>774.0</v>
       </c>
       <c r="O229" t="n">
-        <v>380.0</v>
+        <v>421.0</v>
       </c>
       <c r="P229" t="n">
-        <v>312.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q229" t="n">
         <v>18.0</v>
@@ -16425,7 +16425,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" t="n">
-        <v>361.0</v>
+        <v>381.0</v>
       </c>
       <c r="K230" t="n">
         <v>1.0</v>
@@ -16437,16 +16437,16 @@
         <v>0.0</v>
       </c>
       <c r="N230" t="n">
-        <v>361.0</v>
+        <v>381.0</v>
       </c>
       <c r="O230" t="n">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
       <c r="P230" t="n">
-        <v>162.0</v>
+        <v>174.0</v>
       </c>
       <c r="Q230" t="n">
-        <v>139.0</v>
+        <v>142.0</v>
       </c>
       <c r="R230" t="n">
         <v>0.0</v>
@@ -16567,7 +16567,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" t="n">
-        <v>344.0</v>
+        <v>448.0</v>
       </c>
       <c r="K232" t="n">
         <v>1.0</v>
@@ -16579,16 +16579,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" t="n">
-        <v>344.0</v>
+        <v>448.0</v>
       </c>
       <c r="O232" t="n">
         <v>5.0</v>
       </c>
       <c r="P232" t="n">
-        <v>28.0</v>
+        <v>53.0</v>
       </c>
       <c r="Q232" t="n">
-        <v>311.0</v>
+        <v>390.0</v>
       </c>
       <c r="R232" t="n">
         <v>0.0</v>
@@ -16638,7 +16638,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" t="n">
-        <v>328.0</v>
+        <v>373.0</v>
       </c>
       <c r="K233" t="n">
         <v>1.0</v>
@@ -16650,16 +16650,16 @@
         <v>0.0</v>
       </c>
       <c r="N233" t="n">
-        <v>328.0</v>
+        <v>373.0</v>
       </c>
       <c r="O233" t="n">
         <v>81.0</v>
       </c>
       <c r="P233" t="n">
-        <v>159.0</v>
+        <v>185.0</v>
       </c>
       <c r="Q233" t="n">
-        <v>88.0</v>
+        <v>107.0</v>
       </c>
       <c r="R233" t="n">
         <v>3.0</v>
